--- a/01_Raw_data/RW.log.xlsx
+++ b/01_Raw_data/RW.log.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Howley_Bradford_Streams\Howley_Bradford_Streams\01_Raw_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dissertation\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0D59F3-8B88-4F47-B948-D70437014C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBE8DBB-1A2F-4BF5-8F40-421FC6AF4B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="2" activeTab="7" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
   </bookViews>
   <sheets>
     <sheet name="log" sheetId="1" r:id="rId1"/>
     <sheet name="well dims" sheetId="9" r:id="rId2"/>
-    <sheet name="elevation" sheetId="10" r:id="rId3"/>
-    <sheet name="total well length " sheetId="3" r:id="rId4"/>
-    <sheet name="well heightw extension " sheetId="8" r:id="rId5"/>
-    <sheet name="well height_raw" sheetId="2" r:id="rId6"/>
-    <sheet name="screen extent" sheetId="7" r:id="rId7"/>
+    <sheet name="screen extent" sheetId="7" r:id="rId3"/>
+    <sheet name="elevation" sheetId="10" r:id="rId4"/>
+    <sheet name="total well length " sheetId="3" r:id="rId5"/>
+    <sheet name="well heightw extension " sheetId="8" r:id="rId6"/>
+    <sheet name="well height_raw" sheetId="2" r:id="rId7"/>
     <sheet name="scope elevations" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">log!$A$1:$K$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">log!$A$1:$L$229</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -186,9 +186,6 @@
     <t>Dry; used extension</t>
   </si>
   <si>
-    <t>well.bottom.elevation</t>
-  </si>
-  <si>
     <t>Temp</t>
   </si>
   <si>
@@ -214,6 +211,9 @@
   </si>
   <si>
     <t>scope.surface.elevation</t>
+  </si>
+  <si>
+    <t>DID NOT PUMP</t>
   </si>
 </sst>
 </file>
@@ -610,21 +610,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}">
-  <dimension ref="A1:K229"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L229"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="24.140625" customWidth="1"/>
     <col min="8" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -644,7 +646,7 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -655,11 +657,11 @@
       <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45569</v>
       </c>
@@ -672,9 +674,9 @@
       <c r="E2">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="F2">
-        <f>'well dims'!$H$2+E2</f>
-        <v>4.6190000000000024</v>
+      <c r="F2" t="e">
+        <f>'well dims'!#REF!+E2</f>
+        <v>#REF!</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -682,11 +684,11 @@
       <c r="J2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45569</v>
       </c>
@@ -699,9 +701,9 @@
       <c r="E3">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="F3">
-        <f>'well dims'!$H$3-E3</f>
-        <v>4.0254999999999983</v>
+      <c r="F3" t="e">
+        <f>'well dims'!#REF!-E3</f>
+        <v>#REF!</v>
       </c>
       <c r="H3">
         <v>5.97</v>
@@ -709,11 +711,11 @@
       <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45569</v>
       </c>
@@ -736,11 +738,11 @@
       <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45569</v>
       </c>
@@ -748,14 +750,14 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>0.24</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
         <v>1.62</v>
       </c>
       <c r="E5">
         <f>C5-D5</f>
-        <v>-1.3800000000000001</v>
+        <v>-0.87000000000000011</v>
       </c>
       <c r="H5">
         <v>5.19</v>
@@ -763,11 +765,11 @@
       <c r="J5" t="s">
         <v>8</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45569</v>
       </c>
@@ -784,9 +786,9 @@
         <f>C6-D6</f>
         <v>-0.70000000000000007</v>
       </c>
-      <c r="F6">
-        <f>'well dims'!$H$6+E6</f>
-        <v>3.0040000000000004</v>
+      <c r="F6" t="e">
+        <f>'well dims'!#REF!+E6</f>
+        <v>#REF!</v>
       </c>
       <c r="H6">
         <v>4.2</v>
@@ -794,11 +796,11 @@
       <c r="J6" t="s">
         <v>8</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45569</v>
       </c>
@@ -821,11 +823,11 @@
       <c r="J7" t="s">
         <v>8</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45569</v>
       </c>
@@ -841,11 +843,11 @@
       <c r="J8" t="s">
         <v>8</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45569</v>
       </c>
@@ -868,11 +870,11 @@
       <c r="J9" t="s">
         <v>30</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45569</v>
       </c>
@@ -892,7 +894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45569</v>
       </c>
@@ -909,9 +911,9 @@
         <f>C11-D11</f>
         <v>-1.3049999999999999</v>
       </c>
-      <c r="F11">
-        <f>'well dims'!$H$11+E11</f>
-        <v>-0.78300000000000147</v>
+      <c r="F11" t="e">
+        <f>'well dims'!#REF!+E11</f>
+        <v>#REF!</v>
       </c>
       <c r="H11">
         <v>6.45</v>
@@ -920,7 +922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45569</v>
       </c>
@@ -944,7 +946,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45569</v>
       </c>
@@ -968,7 +970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45569</v>
       </c>
@@ -985,9 +987,9 @@
         <f t="shared" si="0"/>
         <v>-0.77499999999999991</v>
       </c>
-      <c r="F14">
-        <f>'well dims'!$H$14+E14</f>
-        <v>-0.77499999999999991</v>
+      <c r="F14" t="e">
+        <f>'well dims'!#REF!+E14</f>
+        <v>#REF!</v>
       </c>
       <c r="H14">
         <v>3.79</v>
@@ -996,7 +998,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45569</v>
       </c>
@@ -1013,9 +1015,9 @@
         <f t="shared" si="0"/>
         <v>-1.17</v>
       </c>
-      <c r="F15">
-        <f>'well dims'!$H$15+E15</f>
-        <v>2.2599999999999998</v>
+      <c r="F15" t="e">
+        <f>'well dims'!#REF!+E15</f>
+        <v>#REF!</v>
       </c>
       <c r="H15">
         <v>3.93</v>
@@ -1024,7 +1026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45569</v>
       </c>
@@ -1041,9 +1043,9 @@
         <f t="shared" si="0"/>
         <v>-0.47</v>
       </c>
-      <c r="F16">
-        <f>'well dims'!$H$16+E16</f>
-        <v>-0.11600000000000077</v>
+      <c r="F16" t="e">
+        <f>'well dims'!#REF!+E16</f>
+        <v>#REF!</v>
       </c>
       <c r="H16">
         <v>3.88</v>
@@ -1052,7 +1054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>45569</v>
       </c>
@@ -1069,18 +1071,18 @@
         <f t="shared" si="0"/>
         <v>-1.25</v>
       </c>
-      <c r="F17">
-        <f>'well dims'!$H$17+log!E17</f>
-        <v>-0.82399999999999807</v>
+      <c r="F17" t="e">
+        <f>'well dims'!#REF!+log!E17</f>
+        <v>#REF!</v>
       </c>
       <c r="H17">
         <v>4.34</v>
       </c>
       <c r="J17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45687</v>
       </c>
@@ -1097,9 +1099,9 @@
         <f>C18-D18</f>
         <v>2.5000000000000022E-2</v>
       </c>
-      <c r="F18">
-        <f>'well dims'!$H$2+E18</f>
-        <v>4.5790000000000024</v>
+      <c r="F18" t="e">
+        <f>'well dims'!#REF!+E18</f>
+        <v>#REF!</v>
       </c>
       <c r="G18">
         <v>13</v>
@@ -1111,7 +1113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45687</v>
       </c>
@@ -1128,9 +1130,9 @@
         <f>D19-C19</f>
         <v>-0.14499999999999996</v>
       </c>
-      <c r="F19">
-        <f>'well dims'!$H$3-E19</f>
-        <v>4.227999999999998</v>
+      <c r="F19" t="e">
+        <f>'well dims'!#REF!-E19</f>
+        <v>#REF!</v>
       </c>
       <c r="G19">
         <v>12.9</v>
@@ -1142,7 +1144,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>45687</v>
       </c>
@@ -1164,11 +1166,11 @@
       <c r="J20" t="s">
         <v>8</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>45687</v>
       </c>
@@ -1195,7 +1197,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45687</v>
       </c>
@@ -1208,9 +1210,9 @@
       <c r="E22">
         <v>0.04</v>
       </c>
-      <c r="F22">
-        <f>'well dims'!$H$6+E22</f>
-        <v>3.7440000000000007</v>
+      <c r="F22" t="e">
+        <f>'well dims'!#REF!+E22</f>
+        <v>#REF!</v>
       </c>
       <c r="G22">
         <v>14.2</v>
@@ -1222,7 +1224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45687</v>
       </c>
@@ -1249,7 +1251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45687</v>
       </c>
@@ -1272,7 +1274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45687</v>
       </c>
@@ -1295,7 +1297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>45687</v>
       </c>
@@ -1322,7 +1324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>45687</v>
       </c>
@@ -1345,7 +1347,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>45687</v>
       </c>
@@ -1362,9 +1364,9 @@
         <f t="shared" ref="E28:E35" si="1">C28-D28</f>
         <v>-1.32</v>
       </c>
-      <c r="F28">
-        <f>'well dims'!$H$11+E28</f>
-        <v>-0.7980000000000016</v>
+      <c r="F28" t="e">
+        <f>'well dims'!#REF!+E28</f>
+        <v>#REF!</v>
       </c>
       <c r="G28">
         <v>17.100000000000001</v>
@@ -1376,7 +1378,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>45687</v>
       </c>
@@ -1403,7 +1405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>45687</v>
       </c>
@@ -1430,7 +1432,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>45687</v>
       </c>
@@ -1447,9 +1449,9 @@
         <f t="shared" si="1"/>
         <v>-0.28500000000000003</v>
       </c>
-      <c r="F31">
-        <f>'well dims'!$H$14+E31</f>
-        <v>-0.28500000000000003</v>
+      <c r="F31" t="e">
+        <f>'well dims'!#REF!+E31</f>
+        <v>#REF!</v>
       </c>
       <c r="G31">
         <v>13.2</v>
@@ -1461,7 +1463,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>45687</v>
       </c>
@@ -1478,9 +1480,9 @@
         <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
-      <c r="F32">
-        <f>'well dims'!$H$15+E32</f>
-        <v>2.9299999999999997</v>
+      <c r="F32" t="e">
+        <f>'well dims'!#REF!+E32</f>
+        <v>#REF!</v>
       </c>
       <c r="G32">
         <v>16</v>
@@ -1492,7 +1494,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>45687</v>
       </c>
@@ -1509,9 +1511,9 @@
         <f t="shared" si="1"/>
         <v>-0.53499999999999992</v>
       </c>
-      <c r="F33">
-        <f>'well dims'!$H$16+E33</f>
-        <v>-0.18100000000000072</v>
+      <c r="F33" t="e">
+        <f>'well dims'!#REF!+E33</f>
+        <v>#REF!</v>
       </c>
       <c r="G33">
         <v>16.100000000000001</v>
@@ -1523,7 +1525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>45687</v>
       </c>
@@ -1540,9 +1542,9 @@
         <f t="shared" si="1"/>
         <v>-0.72</v>
       </c>
-      <c r="F34">
-        <f>'well dims'!H34+log!E34</f>
-        <v>-0.72</v>
+      <c r="F34" t="e">
+        <f>'well dims'!#REF!+log!E34</f>
+        <v>#REF!</v>
       </c>
       <c r="G34">
         <v>14.5</v>
@@ -1551,10 +1553,10 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>45687</v>
       </c>
@@ -1581,7 +1583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>45728</v>
       </c>
@@ -1598,9 +1600,9 @@
         <f>C36-D36</f>
         <v>-1.5000000000000013E-2</v>
       </c>
-      <c r="F36">
-        <f>'well dims'!$H$2+E36</f>
-        <v>4.5390000000000024</v>
+      <c r="F36" t="e">
+        <f>'well dims'!#REF!+E36</f>
+        <v>#REF!</v>
       </c>
       <c r="G36">
         <v>16.3</v>
@@ -1612,7 +1614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>45728</v>
       </c>
@@ -1628,9 +1630,9 @@
       <c r="E37">
         <v>0.14499999999999999</v>
       </c>
-      <c r="F37">
-        <f>'well dims'!$H$3-E37</f>
-        <v>3.9379999999999984</v>
+      <c r="F37" t="e">
+        <f>'well dims'!#REF!-E37</f>
+        <v>#REF!</v>
       </c>
       <c r="G37">
         <v>16.2</v>
@@ -1642,7 +1644,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>45728</v>
       </c>
@@ -1668,7 +1670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>45728</v>
       </c>
@@ -1695,7 +1697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>45728</v>
       </c>
@@ -1708,9 +1710,9 @@
       <c r="E40">
         <v>0.28100000000000003</v>
       </c>
-      <c r="F40">
-        <f>'well dims'!$H$6+E40</f>
-        <v>3.9850000000000008</v>
+      <c r="F40" t="e">
+        <f>'well dims'!#REF!+E40</f>
+        <v>#REF!</v>
       </c>
       <c r="G40">
         <v>15</v>
@@ -1722,7 +1724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>45728</v>
       </c>
@@ -1749,7 +1751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>45728</v>
       </c>
@@ -1769,7 +1771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>45728</v>
       </c>
@@ -1795,7 +1797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>45728</v>
       </c>
@@ -1822,7 +1824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45728</v>
       </c>
@@ -1848,7 +1850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45728</v>
       </c>
@@ -1865,9 +1867,9 @@
         <f>C46-D46</f>
         <v>-0.35000000000000003</v>
       </c>
-      <c r="F46">
-        <f>'well dims'!$H$11+E46</f>
-        <v>0.17199999999999843</v>
+      <c r="F46" t="e">
+        <f>'well dims'!#REF!+E46</f>
+        <v>#REF!</v>
       </c>
       <c r="G46">
         <v>16.5</v>
@@ -1879,7 +1881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>45728</v>
       </c>
@@ -1933,7 +1935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>45728</v>
       </c>
@@ -1950,9 +1952,9 @@
         <f t="shared" si="2"/>
         <v>-0.11799999999999999</v>
       </c>
-      <c r="F49">
-        <f>'well dims'!$H$14+E49</f>
-        <v>-0.11799999999999999</v>
+      <c r="F49" t="e">
+        <f>'well dims'!#REF!+E49</f>
+        <v>#REF!</v>
       </c>
       <c r="G49">
         <v>15.8</v>
@@ -1964,7 +1966,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45728</v>
       </c>
@@ -1981,9 +1983,9 @@
         <f t="shared" si="2"/>
         <v>-0.38200000000000001</v>
       </c>
-      <c r="F50">
-        <f>'well dims'!$H$15+E50</f>
-        <v>3.0479999999999996</v>
+      <c r="F50" t="e">
+        <f>'well dims'!#REF!+E50</f>
+        <v>#REF!</v>
       </c>
       <c r="G50">
         <v>17.7</v>
@@ -1995,7 +1997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45728</v>
       </c>
@@ -2012,9 +2014,9 @@
         <f t="shared" si="2"/>
         <v>-0.31900000000000001</v>
       </c>
-      <c r="F51">
-        <f>'well dims'!$H$16+E51</f>
-        <v>3.4999999999999198E-2</v>
+      <c r="F51" t="e">
+        <f>'well dims'!#REF!+E51</f>
+        <v>#REF!</v>
       </c>
       <c r="G51">
         <v>18.2</v>
@@ -2026,7 +2028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>45728</v>
       </c>
@@ -2043,9 +2045,9 @@
         <f t="shared" si="2"/>
         <v>3.1000000000000028E-2</v>
       </c>
-      <c r="F52">
-        <f>'well dims'!H52+log!E52</f>
-        <v>3.1000000000000028E-2</v>
+      <c r="F52" t="e">
+        <f>'well dims'!#REF!+log!E52</f>
+        <v>#REF!</v>
       </c>
       <c r="G52">
         <v>16.8</v>
@@ -2057,7 +2059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>45728</v>
       </c>
@@ -2084,7 +2086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>45764</v>
       </c>
@@ -2101,18 +2103,18 @@
         <f>C54-D54</f>
         <v>-0.34000000000000008</v>
       </c>
-      <c r="F54">
-        <f>'well dims'!$H$2+E54</f>
-        <v>4.2140000000000022</v>
+      <c r="F54" t="e">
+        <f>'well dims'!#REF!+E54</f>
+        <v>#REF!</v>
       </c>
       <c r="J54" t="s">
         <v>30</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="L54" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>45764</v>
       </c>
@@ -2129,9 +2131,9 @@
         <f>C56-D55</f>
         <v>7.4999999999999956E-2</v>
       </c>
-      <c r="F55">
-        <f>'well dims'!$H$3-E55</f>
-        <v>4.0079999999999982</v>
+      <c r="F55" t="e">
+        <f>'well dims'!#REF!-E55</f>
+        <v>#REF!</v>
       </c>
       <c r="G55">
         <v>16.5</v>
@@ -2143,7 +2145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>45764</v>
       </c>
@@ -2170,7 +2172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>45764</v>
       </c>
@@ -2197,7 +2199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>45764</v>
       </c>
@@ -2214,9 +2216,9 @@
         <f>C59-D58</f>
         <v>-0.24</v>
       </c>
-      <c r="F58">
-        <f>'well dims'!$H$6+E58</f>
-        <v>3.4640000000000004</v>
+      <c r="F58" t="e">
+        <f>'well dims'!#REF!+E58</f>
+        <v>#REF!</v>
       </c>
       <c r="G58">
         <v>18.600000000000001</v>
@@ -2228,7 +2230,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45764</v>
       </c>
@@ -2255,7 +2257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>45764</v>
       </c>
@@ -2269,7 +2271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>45764</v>
       </c>
@@ -2296,7 +2298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>45764</v>
       </c>
@@ -2323,7 +2325,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>45764</v>
       </c>
@@ -2350,7 +2352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>45764</v>
       </c>
@@ -2367,9 +2369,9 @@
         <f t="shared" si="3"/>
         <v>-0.71</v>
       </c>
-      <c r="F64">
-        <f>'well dims'!$H$11+E64</f>
-        <v>-0.1880000000000015</v>
+      <c r="F64" t="e">
+        <f>'well dims'!#REF!+E64</f>
+        <v>#REF!</v>
       </c>
       <c r="G64">
         <v>18.8</v>
@@ -2381,7 +2383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45764</v>
       </c>
@@ -2408,7 +2410,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45764</v>
       </c>
@@ -2435,7 +2437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45764</v>
       </c>
@@ -2452,9 +2454,9 @@
         <f t="shared" si="3"/>
         <v>-0.625</v>
       </c>
-      <c r="F67">
-        <f>'well dims'!$H$14+E67</f>
-        <v>-0.625</v>
+      <c r="F67" t="e">
+        <f>'well dims'!#REF!+E67</f>
+        <v>#REF!</v>
       </c>
       <c r="G67">
         <v>17.8</v>
@@ -2463,7 +2465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45764</v>
       </c>
@@ -2480,9 +2482,9 @@
         <f t="shared" si="3"/>
         <v>-0.33500000000000002</v>
       </c>
-      <c r="F68">
-        <f>'well dims'!$H$15+E68</f>
-        <v>3.0949999999999998</v>
+      <c r="F68" t="e">
+        <f>'well dims'!#REF!+E68</f>
+        <v>#REF!</v>
       </c>
       <c r="G68">
         <v>19.8</v>
@@ -2491,7 +2493,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>45764</v>
       </c>
@@ -2508,9 +2510,9 @@
         <f t="shared" si="3"/>
         <v>-0.70499999999999996</v>
       </c>
-      <c r="F69">
-        <f>'well dims'!$H$16+E69</f>
-        <v>-0.35100000000000076</v>
+      <c r="F69" t="e">
+        <f>'well dims'!#REF!+E69</f>
+        <v>#REF!</v>
       </c>
       <c r="G69">
         <v>20.2</v>
@@ -2519,7 +2521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>45764</v>
       </c>
@@ -2536,9 +2538,9 @@
         <f t="shared" si="3"/>
         <v>-0.89500000000000002</v>
       </c>
-      <c r="F70">
-        <f>'well dims'!$H$17+log!E70</f>
-        <v>-0.46899999999999809</v>
+      <c r="F70" t="e">
+        <f>'well dims'!#REF!+log!E70</f>
+        <v>#REF!</v>
       </c>
       <c r="G70">
         <v>19.399999999999999</v>
@@ -2547,7 +2549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>45764</v>
       </c>
@@ -2560,11 +2562,11 @@
       <c r="J71" t="s">
         <v>8</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>45400</v>
       </c>
@@ -2581,9 +2583,9 @@
         <f>C72-D72</f>
         <v>-1.1000000000000001</v>
       </c>
-      <c r="F72">
-        <f>'well dims'!$H$2+E72</f>
-        <v>3.454000000000002</v>
+      <c r="F72" t="e">
+        <f>'well dims'!#REF!+E72</f>
+        <v>#REF!</v>
       </c>
       <c r="H72">
         <v>5.41</v>
@@ -2592,7 +2594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>45400</v>
       </c>
@@ -2609,9 +2611,9 @@
         <f t="shared" ref="E73:E86" si="4">C73-D73</f>
         <v>-3.2000000000000028E-2</v>
       </c>
-      <c r="F73">
-        <f>'well dims'!$H$3-E73</f>
-        <v>4.1149999999999984</v>
+      <c r="F73" t="e">
+        <f>'well dims'!#REF!-E73</f>
+        <v>#REF!</v>
       </c>
       <c r="H73">
         <v>5.8</v>
@@ -2620,7 +2622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>45400</v>
       </c>
@@ -2644,7 +2646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>45400</v>
       </c>
@@ -2652,14 +2654,14 @@
         <v>13</v>
       </c>
       <c r="C75">
-        <v>0.24</v>
+        <v>0.75</v>
       </c>
       <c r="D75">
         <v>1.63</v>
       </c>
       <c r="E75">
         <f t="shared" si="4"/>
-        <v>-1.39</v>
+        <v>-0.87999999999999989</v>
       </c>
       <c r="H75">
         <v>6.67</v>
@@ -2668,7 +2670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>45400</v>
       </c>
@@ -2685,9 +2687,9 @@
         <f t="shared" si="4"/>
         <v>-0.77</v>
       </c>
-      <c r="F76">
-        <f>'well dims'!$H$6+E76</f>
-        <v>2.9340000000000006</v>
+      <c r="F76" t="e">
+        <f>'well dims'!#REF!+E76</f>
+        <v>#REF!</v>
       </c>
       <c r="H76">
         <v>6.2</v>
@@ -2696,7 +2698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>45400</v>
       </c>
@@ -2704,20 +2706,20 @@
         <v>15</v>
       </c>
       <c r="C77">
-        <v>8.5000000000000006E-2</v>
+        <v>0.79</v>
       </c>
       <c r="D77">
         <v>1.33</v>
       </c>
       <c r="E77">
         <f t="shared" si="4"/>
-        <v>-1.2450000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="J77" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>45400</v>
       </c>
@@ -2741,7 +2743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>45400</v>
       </c>
@@ -2764,7 +2766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>45400</v>
       </c>
@@ -2781,9 +2783,9 @@
         <f t="shared" si="4"/>
         <v>-1.38</v>
       </c>
-      <c r="F80">
-        <f>'well dims'!$H$11+E80</f>
-        <v>-0.85800000000000143</v>
+      <c r="F80" t="e">
+        <f>'well dims'!#REF!+E80</f>
+        <v>#REF!</v>
       </c>
       <c r="H80">
         <v>5.0999999999999996</v>
@@ -2792,7 +2794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>45400</v>
       </c>
@@ -2816,7 +2818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>45400</v>
       </c>
@@ -2837,7 +2839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>45400</v>
       </c>
@@ -2854,9 +2856,9 @@
         <f t="shared" si="4"/>
         <v>-0.29000000000000004</v>
       </c>
-      <c r="F83">
-        <f>'well dims'!$H$14+E83</f>
-        <v>-0.29000000000000004</v>
+      <c r="F83" t="e">
+        <f>'well dims'!#REF!+E83</f>
+        <v>#REF!</v>
       </c>
       <c r="H83">
         <v>4.7699999999999996</v>
@@ -2865,7 +2867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>45400</v>
       </c>
@@ -2882,9 +2884,9 @@
         <f t="shared" si="4"/>
         <v>-0.83</v>
       </c>
-      <c r="F84">
-        <f>'well dims'!$H$15+E84</f>
-        <v>2.5999999999999996</v>
+      <c r="F84" t="e">
+        <f>'well dims'!#REF!+E84</f>
+        <v>#REF!</v>
       </c>
       <c r="H84">
         <v>4.72</v>
@@ -2893,7 +2895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>45400</v>
       </c>
@@ -2910,9 +2912,9 @@
         <f t="shared" si="4"/>
         <v>-0.59000000000000008</v>
       </c>
-      <c r="F85">
-        <f>'well dims'!$H$16+E85</f>
-        <v>-0.23600000000000088</v>
+      <c r="F85" t="e">
+        <f>'well dims'!#REF!+E85</f>
+        <v>#REF!</v>
       </c>
       <c r="H85">
         <v>4.84</v>
@@ -2921,7 +2923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45400</v>
       </c>
@@ -2938,9 +2940,9 @@
         <f t="shared" si="4"/>
         <v>-0.82999999999999985</v>
       </c>
-      <c r="F86">
-        <f>'well dims'!$H$17+log!E86</f>
-        <v>-0.40399999999999792</v>
+      <c r="F86" t="e">
+        <f>'well dims'!#REF!+log!E86</f>
+        <v>#REF!</v>
       </c>
       <c r="H86">
         <v>5.18</v>
@@ -2949,7 +2951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>45463</v>
       </c>
@@ -2966,15 +2968,16 @@
         <f>C87-D87</f>
         <v>-0.6100000000000001</v>
       </c>
-      <c r="F87">
-        <f>'well dims'!$H$2+E87</f>
-        <v>3.9440000000000017</v>
+      <c r="F87" t="e">
+        <f>'well dims'!#REF!+E87</f>
+        <v>#REF!</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K87" s="3"/>
+    </row>
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>45457</v>
       </c>
@@ -2991,15 +2994,15 @@
         <f t="shared" ref="E88:E100" si="5">C88-D88</f>
         <v>-0.55499999999999994</v>
       </c>
-      <c r="F88">
-        <f>'well dims'!$H$3-E88</f>
-        <v>4.6379999999999981</v>
+      <c r="F88" t="e">
+        <f>'well dims'!#REF!-E88</f>
+        <v>#REF!</v>
       </c>
       <c r="J88" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>45462</v>
       </c>
@@ -3025,8 +3028,9 @@
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K89" s="3"/>
+    </row>
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>45463</v>
       </c>
@@ -3050,7 +3054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>45462</v>
       </c>
@@ -3067,15 +3071,16 @@
         <f t="shared" si="5"/>
         <v>-0.78</v>
       </c>
-      <c r="F91">
-        <f>'well dims'!$H$6+E91</f>
-        <v>2.9240000000000004</v>
+      <c r="F91" t="e">
+        <f>'well dims'!#REF!+E91</f>
+        <v>#REF!</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K91" s="3"/>
+    </row>
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>45463</v>
       </c>
@@ -3093,10 +3098,10 @@
         <v>-1.2250000000000001</v>
       </c>
       <c r="J92" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>45462</v>
       </c>
@@ -3104,7 +3109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>45463</v>
       </c>
@@ -3128,7 +3133,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>45463</v>
       </c>
@@ -3152,7 +3157,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>45463</v>
       </c>
@@ -3194,7 +3199,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>45463</v>
       </c>
@@ -3211,15 +3216,15 @@
         <f t="shared" si="5"/>
         <v>-0.86999999999999988</v>
       </c>
-      <c r="F98">
-        <f>'well dims'!$H$14+E98</f>
-        <v>-0.86999999999999988</v>
+      <c r="F98" t="e">
+        <f>'well dims'!#REF!+E98</f>
+        <v>#REF!</v>
       </c>
       <c r="J98" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>45463</v>
       </c>
@@ -3236,15 +3241,15 @@
         <f t="shared" si="5"/>
         <v>-1.77</v>
       </c>
-      <c r="F99">
-        <f>'well dims'!$H$15+E99</f>
-        <v>1.6599999999999997</v>
+      <c r="F99" t="e">
+        <f>'well dims'!#REF!+E99</f>
+        <v>#REF!</v>
       </c>
       <c r="J99" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>45463</v>
       </c>
@@ -3261,15 +3266,15 @@
         <f t="shared" si="5"/>
         <v>-1.25</v>
       </c>
-      <c r="F100">
-        <f>'well dims'!$H$17+log!E100</f>
-        <v>-0.82399999999999807</v>
+      <c r="F100" t="e">
+        <f>'well dims'!#REF!+log!E100</f>
+        <v>#REF!</v>
       </c>
       <c r="J100" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>45484</v>
       </c>
@@ -3283,9 +3288,9 @@
         <f>C101-D101</f>
         <v>0.44</v>
       </c>
-      <c r="F101">
-        <f>'well dims'!$H$2+E101</f>
-        <v>4.9940000000000024</v>
+      <c r="F101" t="e">
+        <f>'well dims'!#REF!+E101</f>
+        <v>#REF!</v>
       </c>
       <c r="G101">
         <v>26</v>
@@ -3297,7 +3302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>45484</v>
       </c>
@@ -3310,9 +3315,9 @@
       <c r="E102">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F102">
-        <f>'well dims'!$H$3-E102</f>
-        <v>4.0129999999999981</v>
+      <c r="F102" t="e">
+        <f>'well dims'!#REF!-E102</f>
+        <v>#REF!</v>
       </c>
       <c r="G102">
         <v>25.7</v>
@@ -3324,7 +3329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>45484</v>
       </c>
@@ -3347,7 +3352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>45484</v>
       </c>
@@ -3373,7 +3378,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>45484</v>
       </c>
@@ -3386,9 +3391,9 @@
       <c r="E105">
         <v>0.16</v>
       </c>
-      <c r="F105">
-        <f>'well dims'!$H$6+E105</f>
-        <v>3.8640000000000008</v>
+      <c r="F105" t="e">
+        <f>'well dims'!#REF!+E105</f>
+        <v>#REF!</v>
       </c>
       <c r="G105">
         <v>25.9</v>
@@ -3400,7 +3405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>45484</v>
       </c>
@@ -3427,7 +3432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>45484</v>
       </c>
@@ -3447,7 +3452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>45484</v>
       </c>
@@ -3474,7 +3479,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>45484</v>
       </c>
@@ -3525,7 +3530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>45484</v>
       </c>
@@ -3539,10 +3544,10 @@
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>45484</v>
       </c>
@@ -3555,9 +3560,9 @@
       <c r="E112">
         <v>0.05</v>
       </c>
-      <c r="F112">
-        <f>'well dims'!$H$15+E112</f>
-        <v>3.4799999999999995</v>
+      <c r="F112" t="e">
+        <f>'well dims'!#REF!+E112</f>
+        <v>#REF!</v>
       </c>
       <c r="G112">
         <v>28.7</v>
@@ -3569,7 +3574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>45484</v>
       </c>
@@ -3582,9 +3587,9 @@
       <c r="E113">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F113">
-        <f>'well dims'!$H$16+E113</f>
-        <v>0.49399999999999922</v>
+      <c r="F113" t="e">
+        <f>'well dims'!#REF!+E113</f>
+        <v>#REF!</v>
       </c>
       <c r="G113">
         <v>30.6</v>
@@ -3596,7 +3601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>45484</v>
       </c>
@@ -3606,15 +3611,15 @@
       <c r="C114">
         <v>2.25</v>
       </c>
-      <c r="F114">
-        <f>'well dims'!H115+log!E114</f>
-        <v>0</v>
+      <c r="F114" t="e">
+        <f>'well dims'!#REF!+log!E114</f>
+        <v>#REF!</v>
       </c>
       <c r="J114" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>45635</v>
       </c>
@@ -3631,9 +3636,9 @@
         <f>C115-D115</f>
         <v>-0.6100000000000001</v>
       </c>
-      <c r="F115">
-        <f>'well dims'!$H$2+E115</f>
-        <v>3.9440000000000017</v>
+      <c r="F115" t="e">
+        <f>'well dims'!#REF!+E115</f>
+        <v>#REF!</v>
       </c>
       <c r="G115">
         <v>15.9</v>
@@ -3645,7 +3650,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>45635</v>
       </c>
@@ -3661,9 +3666,9 @@
       <c r="E116">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="F116">
-        <f>'well dims'!$H$3-E116</f>
-        <v>4.0254999999999983</v>
+      <c r="F116" t="e">
+        <f>'well dims'!#REF!-E116</f>
+        <v>#REF!</v>
       </c>
       <c r="G116">
         <v>17</v>
@@ -3675,7 +3680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>45635</v>
       </c>
@@ -3702,7 +3707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>45635</v>
       </c>
@@ -3729,7 +3734,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>45635</v>
       </c>
@@ -3746,9 +3751,9 @@
         <f t="shared" si="7"/>
         <v>-0.26</v>
       </c>
-      <c r="F119">
-        <f>'well dims'!$H$6+E119</f>
-        <v>3.4440000000000008</v>
+      <c r="F119" t="e">
+        <f>'well dims'!#REF!+E119</f>
+        <v>#REF!</v>
       </c>
       <c r="G119">
         <v>17.8</v>
@@ -3760,7 +3765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>45635</v>
       </c>
@@ -3787,7 +3792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>45635</v>
       </c>
@@ -3808,7 +3813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>45635</v>
       </c>
@@ -3835,7 +3840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>45635</v>
       </c>
@@ -3862,7 +3867,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>45635</v>
       </c>
@@ -3889,7 +3894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>45635</v>
       </c>
@@ -3906,9 +3911,9 @@
         <f t="shared" si="7"/>
         <v>-1.01</v>
       </c>
-      <c r="F125">
-        <f>'well dims'!$H$11+E125</f>
-        <v>-0.48800000000000154</v>
+      <c r="F125" t="e">
+        <f>'well dims'!#REF!+E125</f>
+        <v>#REF!</v>
       </c>
       <c r="G125">
         <v>20.2</v>
@@ -3920,7 +3925,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>45635</v>
       </c>
@@ -3974,7 +3979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>45635</v>
       </c>
@@ -3991,9 +3996,9 @@
         <f t="shared" si="7"/>
         <v>-0.35</v>
       </c>
-      <c r="F128">
-        <f>'well dims'!$H$14+E128</f>
-        <v>-0.35</v>
+      <c r="F128" t="e">
+        <f>'well dims'!#REF!+E128</f>
+        <v>#REF!</v>
       </c>
       <c r="G128">
         <v>14.8</v>
@@ -4005,7 +4010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>45635</v>
       </c>
@@ -4022,9 +4027,9 @@
         <f t="shared" si="7"/>
         <v>-0.65</v>
       </c>
-      <c r="F129">
-        <f>'well dims'!$H$15+E129</f>
-        <v>2.78</v>
+      <c r="F129" t="e">
+        <f>'well dims'!#REF!+E129</f>
+        <v>#REF!</v>
       </c>
       <c r="G129">
         <v>20</v>
@@ -4036,7 +4041,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>45635</v>
       </c>
@@ -4053,9 +4058,9 @@
         <f t="shared" si="7"/>
         <v>-0.72</v>
       </c>
-      <c r="F130">
-        <f>'well dims'!$H$16+E130</f>
-        <v>-0.36600000000000077</v>
+      <c r="F130" t="e">
+        <f>'well dims'!#REF!+E130</f>
+        <v>#REF!</v>
       </c>
       <c r="G130">
         <v>19.8</v>
@@ -4067,7 +4072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>45635</v>
       </c>
@@ -4084,9 +4089,9 @@
         <f t="shared" si="7"/>
         <v>-1.03</v>
       </c>
-      <c r="F131">
-        <f>'well dims'!$H$17+log!E131</f>
-        <v>-0.60399999999999809</v>
+      <c r="F131" t="e">
+        <f>'well dims'!#REF!+log!E131</f>
+        <v>#REF!</v>
       </c>
       <c r="G131">
         <v>18.5</v>
@@ -4098,7 +4103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>45635</v>
       </c>
@@ -4125,7 +4130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>45667</v>
       </c>
@@ -4142,15 +4147,15 @@
         <f>C133-D133</f>
         <v>-0.56000000000000005</v>
       </c>
-      <c r="F133">
-        <f>'well dims'!$H$2+E133</f>
-        <v>3.994000000000002</v>
+      <c r="F133" t="e">
+        <f>'well dims'!#REF!+E133</f>
+        <v>#REF!</v>
       </c>
       <c r="J133" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>45667</v>
       </c>
@@ -4167,9 +4172,9 @@
         <f t="shared" ref="E134:E138" si="8">C134-D134</f>
         <v>-0.34</v>
       </c>
-      <c r="F134">
-        <f>'well dims'!$H$3-E134</f>
-        <v>4.4229999999999983</v>
+      <c r="F134" t="e">
+        <f>'well dims'!#REF!-E134</f>
+        <v>#REF!</v>
       </c>
       <c r="G134">
         <v>15.2</v>
@@ -4181,7 +4186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>45667</v>
       </c>
@@ -4208,7 +4213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>45667</v>
       </c>
@@ -4235,7 +4240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>45667</v>
       </c>
@@ -4252,9 +4257,9 @@
         <f t="shared" si="8"/>
         <v>-7.9999999999999988E-2</v>
       </c>
-      <c r="F137">
-        <f>'well dims'!$H$6+E137</f>
-        <v>3.6240000000000006</v>
+      <c r="F137" t="e">
+        <f>'well dims'!#REF!+E137</f>
+        <v>#REF!</v>
       </c>
       <c r="G137">
         <v>15.9</v>
@@ -4266,7 +4271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>45667</v>
       </c>
@@ -4293,7 +4298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>45667</v>
       </c>
@@ -4317,7 +4322,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>45667</v>
       </c>
@@ -4338,7 +4343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>45667</v>
       </c>
@@ -4365,7 +4370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>45667</v>
       </c>
@@ -4389,10 +4394,10 @@
         <v>4.45</v>
       </c>
       <c r="J142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>45667</v>
       </c>
@@ -4409,9 +4414,9 @@
         <f t="shared" si="9"/>
         <v>-0.14000000000000001</v>
       </c>
-      <c r="F143">
-        <f>'well dims'!$H$11+E143</f>
-        <v>0.38199999999999845</v>
+      <c r="F143" t="e">
+        <f>'well dims'!#REF!+E143</f>
+        <v>#REF!</v>
       </c>
       <c r="G143">
         <v>18.8</v>
@@ -4423,7 +4428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>45667</v>
       </c>
@@ -4450,7 +4455,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>45667</v>
       </c>
@@ -4460,11 +4465,14 @@
       <c r="C145">
         <v>0.25</v>
       </c>
+      <c r="E145">
+        <v>-4.3</v>
+      </c>
       <c r="J145" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>45667</v>
       </c>
@@ -4481,9 +4489,9 @@
         <f>C146-D146</f>
         <v>-0.495</v>
       </c>
-      <c r="F146">
-        <f>'well dims'!$H$14+E146</f>
-        <v>-0.495</v>
+      <c r="F146" t="e">
+        <f>'well dims'!#REF!+E146</f>
+        <v>#REF!</v>
       </c>
       <c r="G146">
         <v>13</v>
@@ -4495,7 +4503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>45667</v>
       </c>
@@ -4512,9 +4520,9 @@
         <f t="shared" ref="E147:E150" si="10">C147-D147</f>
         <v>-0.5</v>
       </c>
-      <c r="F147">
-        <f>'well dims'!$H$15+E147</f>
-        <v>2.9299999999999997</v>
+      <c r="F147" t="e">
+        <f>'well dims'!#REF!+E147</f>
+        <v>#REF!</v>
       </c>
       <c r="G147">
         <v>17.899999999999999</v>
@@ -4526,7 +4534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>45667</v>
       </c>
@@ -4543,9 +4551,9 @@
         <f t="shared" si="10"/>
         <v>-0.84</v>
       </c>
-      <c r="F148">
-        <f>'well dims'!$H$16+E148</f>
-        <v>-0.48600000000000076</v>
+      <c r="F148" t="e">
+        <f>'well dims'!#REF!+E148</f>
+        <v>#REF!</v>
       </c>
       <c r="G148">
         <v>18</v>
@@ -4557,7 +4565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>45667</v>
       </c>
@@ -4574,9 +4582,9 @@
         <f>C149-D149</f>
         <v>-0.29999999999999982</v>
       </c>
-      <c r="F149">
-        <f>'well dims'!$H$17+log!E149</f>
-        <v>0.12600000000000211</v>
+      <c r="F149" t="e">
+        <f>'well dims'!#REF!+log!E149</f>
+        <v>#REF!</v>
       </c>
       <c r="G149">
         <v>16.600000000000001</v>
@@ -4587,11 +4595,11 @@
       <c r="J149" t="s">
         <v>8</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>45667</v>
       </c>
@@ -4618,7 +4626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>45502</v>
       </c>
@@ -4632,9 +4640,9 @@
         <f>C151-D151</f>
         <v>0.44</v>
       </c>
-      <c r="F151">
-        <f>'well dims'!$H$2+E151</f>
-        <v>4.9940000000000024</v>
+      <c r="F151" t="e">
+        <f>'well dims'!#REF!+E151</f>
+        <v>#REF!</v>
       </c>
       <c r="G151">
         <v>25.8</v>
@@ -4646,7 +4654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>45502</v>
       </c>
@@ -4659,9 +4667,9 @@
       <c r="E152">
         <v>0.23499999999999999</v>
       </c>
-      <c r="F152">
-        <f>'well dims'!$H$3-E152</f>
-        <v>3.8479999999999985</v>
+      <c r="F152" t="e">
+        <f>'well dims'!#REF!-E152</f>
+        <v>#REF!</v>
       </c>
       <c r="G152">
         <v>26</v>
@@ -4673,7 +4681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>45502</v>
       </c>
@@ -4696,7 +4704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>45502</v>
       </c>
@@ -4723,7 +4731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>45502</v>
       </c>
@@ -4736,9 +4744,9 @@
       <c r="E155">
         <v>0.36</v>
       </c>
-      <c r="F155">
-        <f>'well dims'!$H$6+E155</f>
-        <v>4.0640000000000009</v>
+      <c r="F155" t="e">
+        <f>'well dims'!#REF!+E155</f>
+        <v>#REF!</v>
       </c>
       <c r="G155">
         <v>25.72</v>
@@ -4750,7 +4758,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>45502</v>
       </c>
@@ -4777,7 +4785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>45502</v>
       </c>
@@ -4804,7 +4812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>45502</v>
       </c>
@@ -4831,7 +4839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>45502</v>
       </c>
@@ -4848,9 +4856,9 @@
         <f t="shared" si="11"/>
         <v>-1.9999999999999997E-2</v>
       </c>
-      <c r="F159">
-        <f>'well dims'!$H$11+E159</f>
-        <v>0.50199999999999845</v>
+      <c r="F159" t="e">
+        <f>'well dims'!#REF!+E159</f>
+        <v>#REF!</v>
       </c>
       <c r="G159">
         <v>29.26</v>
@@ -4862,7 +4870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>45502</v>
       </c>
@@ -4896,11 +4904,14 @@
       <c r="B161" t="s">
         <v>21</v>
       </c>
+      <c r="E161">
+        <v>-4.3</v>
+      </c>
       <c r="J161" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>45502</v>
       </c>
@@ -4917,9 +4928,9 @@
         <f>C162-D162</f>
         <v>-0.28000000000000003</v>
       </c>
-      <c r="F162">
-        <f>'well dims'!$H$14+E162</f>
-        <v>-0.28000000000000003</v>
+      <c r="F162" t="e">
+        <f>'well dims'!#REF!+E162</f>
+        <v>#REF!</v>
       </c>
       <c r="G162">
         <v>28</v>
@@ -4931,7 +4942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>45502</v>
       </c>
@@ -4948,9 +4959,9 @@
         <f t="shared" ref="E163:E165" si="12">C163-D163</f>
         <v>-0.59</v>
       </c>
-      <c r="F163">
-        <f>'well dims'!$H$15+E163</f>
-        <v>2.84</v>
+      <c r="F163" t="e">
+        <f>'well dims'!#REF!+E163</f>
+        <v>#REF!</v>
       </c>
       <c r="G163">
         <v>28</v>
@@ -4962,7 +4973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>45502</v>
       </c>
@@ -4979,9 +4990,9 @@
         <f t="shared" si="12"/>
         <v>-0.77</v>
       </c>
-      <c r="F164">
-        <f>'well dims'!$H$16+E164</f>
-        <v>-0.41600000000000081</v>
+      <c r="F164" t="e">
+        <f>'well dims'!#REF!+E164</f>
+        <v>#REF!</v>
       </c>
       <c r="G164">
         <v>28</v>
@@ -4993,7 +5004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>45502</v>
       </c>
@@ -5010,15 +5021,15 @@
         <f t="shared" si="12"/>
         <v>-1.0499999999999998</v>
       </c>
-      <c r="F165">
-        <f>'well dims'!$H$17+log!E165</f>
-        <v>-0.62399999999999789</v>
+      <c r="F165" t="e">
+        <f>'well dims'!#REF!+log!E165</f>
+        <v>#REF!</v>
       </c>
       <c r="J165" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>45534</v>
       </c>
@@ -5031,9 +5042,9 @@
       <c r="E166">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="F166">
-        <f>'well dims'!$H$2+E166</f>
-        <v>4.6100000000000021</v>
+      <c r="F166" t="e">
+        <f>'well dims'!#REF!+E166</f>
+        <v>#REF!</v>
       </c>
       <c r="G166">
         <v>26.04</v>
@@ -5045,7 +5056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>45534</v>
       </c>
@@ -5058,9 +5069,9 @@
       <c r="E167">
         <v>0.25</v>
       </c>
-      <c r="F167">
-        <f>'well dims'!$H$3-E167</f>
-        <v>3.8329999999999984</v>
+      <c r="F167" t="e">
+        <f>'well dims'!#REF!-E167</f>
+        <v>#REF!</v>
       </c>
       <c r="G167">
         <v>26.2</v>
@@ -5072,7 +5083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>45534</v>
       </c>
@@ -5099,7 +5110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>45534</v>
       </c>
@@ -5126,7 +5137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>45534</v>
       </c>
@@ -5143,9 +5154,9 @@
         <f>C170-D170</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="F170">
-        <f>'well dims'!$H$6+E170</f>
-        <v>3.7440000000000007</v>
+      <c r="F170" t="e">
+        <f>'well dims'!#REF!+E170</f>
+        <v>#REF!</v>
       </c>
       <c r="G170">
         <v>26.43</v>
@@ -5157,7 +5168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>45534</v>
       </c>
@@ -5177,7 +5188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>45534</v>
       </c>
@@ -5194,7 +5205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>45534</v>
       </c>
@@ -5214,7 +5225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>45534</v>
       </c>
@@ -5237,7 +5248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>45534</v>
       </c>
@@ -5250,9 +5261,9 @@
       <c r="E175">
         <v>-0.51</v>
       </c>
-      <c r="F175">
-        <f>'well dims'!$H$11+E175</f>
-        <v>1.1999999999998456E-2</v>
+      <c r="F175" t="e">
+        <f>'well dims'!#REF!+E175</f>
+        <v>#REF!</v>
       </c>
       <c r="G175">
         <v>26.23</v>
@@ -5264,7 +5275,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>45534</v>
       </c>
@@ -5311,7 +5322,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>45534</v>
       </c>
@@ -5322,9 +5333,9 @@
         <f>0.24-0.4</f>
         <v>-0.16000000000000003</v>
       </c>
-      <c r="F178">
-        <f>'well dims'!$H$14+E178</f>
-        <v>-0.16000000000000003</v>
+      <c r="F178" t="e">
+        <f>'well dims'!#REF!+E178</f>
+        <v>#REF!</v>
       </c>
       <c r="G178">
         <v>29.07</v>
@@ -5336,7 +5347,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>45534</v>
       </c>
@@ -5346,9 +5357,9 @@
       <c r="E179">
         <v>-0.4</v>
       </c>
-      <c r="F179">
-        <f>'well dims'!$H$15+E179</f>
-        <v>3.03</v>
+      <c r="F179" t="e">
+        <f>'well dims'!#REF!+E179</f>
+        <v>#REF!</v>
       </c>
       <c r="G179">
         <v>28.69</v>
@@ -5360,7 +5371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>45534</v>
       </c>
@@ -5370,9 +5381,9 @@
       <c r="E180">
         <v>-0.39</v>
       </c>
-      <c r="F180">
-        <f>'well dims'!$H$16+E180</f>
-        <v>-3.6000000000000809E-2</v>
+      <c r="F180" t="e">
+        <f>'well dims'!#REF!+E180</f>
+        <v>#REF!</v>
       </c>
       <c r="G180">
         <v>30</v>
@@ -5384,7 +5395,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>45534</v>
       </c>
@@ -5395,15 +5406,15 @@
         <f>0.31-0.86</f>
         <v>-0.55000000000000004</v>
       </c>
-      <c r="F181">
-        <f>'well dims'!H182+log!E181</f>
-        <v>-0.55000000000000004</v>
+      <c r="F181" t="e">
+        <f>'well dims'!#REF!+log!E181</f>
+        <v>#REF!</v>
       </c>
       <c r="J181" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>45442</v>
       </c>
@@ -5420,15 +5431,15 @@
         <f>C182-D182</f>
         <v>-0.59000000000000008</v>
       </c>
-      <c r="F182">
-        <f>'well dims'!$H$2+E182</f>
-        <v>3.9640000000000022</v>
+      <c r="F182" t="e">
+        <f>'well dims'!#REF!+E182</f>
+        <v>#REF!</v>
       </c>
       <c r="J182" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>45442</v>
       </c>
@@ -5445,9 +5456,9 @@
         <f t="shared" ref="E183:E196" si="13">C183-D183</f>
         <v>-0.35500000000000004</v>
       </c>
-      <c r="F183">
-        <f>'well dims'!$H$3-E183</f>
-        <v>4.4379999999999988</v>
+      <c r="F183" t="e">
+        <f>'well dims'!#REF!-E183</f>
+        <v>#REF!</v>
       </c>
       <c r="H183">
         <v>6.4</v>
@@ -5456,7 +5467,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>45442</v>
       </c>
@@ -5480,7 +5491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>45442</v>
       </c>
@@ -5504,7 +5515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>45442</v>
       </c>
@@ -5521,9 +5532,9 @@
         <f t="shared" si="13"/>
         <v>-0.38</v>
       </c>
-      <c r="F186">
-        <f>'well dims'!$H$6+E186</f>
-        <v>3.3240000000000007</v>
+      <c r="F186" t="e">
+        <f>'well dims'!#REF!+E186</f>
+        <v>#REF!</v>
       </c>
       <c r="H186">
         <v>6.13</v>
@@ -5532,7 +5543,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>45442</v>
       </c>
@@ -5556,7 +5567,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>45442</v>
       </c>
@@ -5564,11 +5575,14 @@
         <v>17</v>
       </c>
       <c r="C188" s="3"/>
+      <c r="E188">
+        <v>-2.25</v>
+      </c>
       <c r="J188" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>45442</v>
       </c>
@@ -5580,7 +5594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>45442</v>
       </c>
@@ -5597,15 +5611,15 @@
         <f t="shared" si="13"/>
         <v>-1.155</v>
       </c>
-      <c r="F190">
-        <f>'well dims'!$H$11+E190</f>
-        <v>-0.63300000000000156</v>
+      <c r="F190" t="e">
+        <f>'well dims'!#REF!+E190</f>
+        <v>#REF!</v>
       </c>
       <c r="J190" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>45442</v>
       </c>
@@ -5625,11 +5639,14 @@
         <v>21</v>
       </c>
       <c r="C192" s="3"/>
+      <c r="E192">
+        <v>-4.3</v>
+      </c>
       <c r="J192" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>45442</v>
       </c>
@@ -5646,9 +5663,9 @@
         <f t="shared" si="13"/>
         <v>-0.75</v>
       </c>
-      <c r="F193">
-        <f>'well dims'!$H$14+E193</f>
-        <v>-0.75</v>
+      <c r="F193" t="e">
+        <f>'well dims'!#REF!+E193</f>
+        <v>#REF!</v>
       </c>
       <c r="H193">
         <v>4.6500000000000004</v>
@@ -5657,7 +5674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>45442</v>
       </c>
@@ -5674,15 +5691,15 @@
         <f t="shared" si="13"/>
         <v>-1.24</v>
       </c>
-      <c r="F194">
-        <f>'well dims'!$H$15+E194</f>
-        <v>2.1899999999999995</v>
+      <c r="F194" t="e">
+        <f>'well dims'!#REF!+E194</f>
+        <v>#REF!</v>
       </c>
       <c r="J194" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>45442</v>
       </c>
@@ -5699,9 +5716,9 @@
         <f t="shared" si="13"/>
         <v>-0.88</v>
       </c>
-      <c r="F195">
-        <f>'well dims'!$H$16+E195</f>
-        <v>-0.5260000000000008</v>
+      <c r="F195" t="e">
+        <f>'well dims'!#REF!+E195</f>
+        <v>#REF!</v>
       </c>
       <c r="H195">
         <v>4.03</v>
@@ -5710,7 +5727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>45442</v>
       </c>
@@ -5727,9 +5744,9 @@
         <f t="shared" si="13"/>
         <v>-1.17</v>
       </c>
-      <c r="F196">
-        <f>'well dims'!$H$17+log!E196</f>
-        <v>-0.743999999999998</v>
+      <c r="F196" t="e">
+        <f>'well dims'!#REF!+log!E196</f>
+        <v>#REF!</v>
       </c>
       <c r="H196">
         <v>3.66</v>
@@ -5738,7 +5755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>45940</v>
       </c>
@@ -5755,9 +5772,9 @@
         <f>C197-D197</f>
         <v>-0.91000000000000014</v>
       </c>
-      <c r="F197">
-        <f>'well dims'!$H$2+E197</f>
-        <v>3.6440000000000019</v>
+      <c r="F197" t="e">
+        <f>'well dims'!#REF!+E197</f>
+        <v>#REF!</v>
       </c>
       <c r="G197">
         <v>22.1</v>
@@ -5769,7 +5786,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>45940</v>
       </c>
@@ -5786,9 +5803,9 @@
         <f t="shared" ref="E198:E219" si="14">C198-D198</f>
         <v>-0.29499999999999998</v>
       </c>
-      <c r="F198">
-        <f>'well dims'!$H$3-E198</f>
-        <v>4.3779999999999983</v>
+      <c r="F198" t="e">
+        <f>'well dims'!#REF!-E198</f>
+        <v>#REF!</v>
       </c>
       <c r="G198">
         <v>23.3</v>
@@ -5803,7 +5820,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>45940</v>
       </c>
@@ -5830,7 +5847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>45940</v>
       </c>
@@ -5860,7 +5877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>45940</v>
       </c>
@@ -5877,9 +5894,9 @@
         <f t="shared" si="14"/>
         <v>-0.21</v>
       </c>
-      <c r="F201">
-        <f>'well dims'!$H$6+E201</f>
-        <v>3.4940000000000007</v>
+      <c r="F201" t="e">
+        <f>'well dims'!#REF!+E201</f>
+        <v>#REF!</v>
       </c>
       <c r="G201">
         <v>23.3</v>
@@ -5894,7 +5911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>45940</v>
       </c>
@@ -5924,7 +5941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>45940</v>
       </c>
@@ -5954,7 +5971,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>45940</v>
       </c>
@@ -5975,7 +5992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>45940</v>
       </c>
@@ -5996,7 +6013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>45940</v>
       </c>
@@ -6023,7 +6040,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>45940</v>
       </c>
@@ -6074,7 +6091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>45940</v>
       </c>
@@ -6091,15 +6108,15 @@
         <f t="shared" si="14"/>
         <v>-0.875</v>
       </c>
-      <c r="F209">
-        <f>'well dims'!$H$14+E209</f>
-        <v>-0.875</v>
+      <c r="F209" t="e">
+        <f>'well dims'!#REF!+E209</f>
+        <v>#REF!</v>
       </c>
       <c r="J209" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>45940</v>
       </c>
@@ -6116,9 +6133,9 @@
         <f t="shared" si="14"/>
         <v>-1.32</v>
       </c>
-      <c r="F210">
-        <f>'well dims'!$H$15+E210</f>
-        <v>2.1099999999999994</v>
+      <c r="F210" t="e">
+        <f>'well dims'!#REF!+E210</f>
+        <v>#REF!</v>
       </c>
       <c r="G210">
         <v>23.6</v>
@@ -6133,7 +6150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>45940</v>
       </c>
@@ -6144,10 +6161,10 @@
         <v>0</v>
       </c>
       <c r="J211" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>45940</v>
       </c>
@@ -6164,15 +6181,15 @@
         <f t="shared" si="14"/>
         <v>-1.23</v>
       </c>
-      <c r="F212">
-        <f>'well dims'!$H$17+log!E212</f>
-        <v>-0.80399999999999805</v>
+      <c r="F212" t="e">
+        <f>'well dims'!#REF!+log!E212</f>
+        <v>#REF!</v>
       </c>
       <c r="J212" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>45940</v>
       </c>
@@ -6202,7 +6219,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>45597</v>
       </c>
@@ -6229,7 +6246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>45597</v>
       </c>
@@ -6256,7 +6273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>45597</v>
       </c>
@@ -6283,7 +6300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>45597</v>
       </c>
@@ -6291,14 +6308,14 @@
         <v>13</v>
       </c>
       <c r="C217">
-        <v>0.24</v>
+        <v>0.75</v>
       </c>
       <c r="D217">
         <v>1.95</v>
       </c>
       <c r="E217">
         <f t="shared" si="14"/>
-        <v>-1.71</v>
+        <v>-1.2</v>
       </c>
       <c r="G217">
         <v>22.3</v>
@@ -6310,7 +6327,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>45597</v>
       </c>
@@ -6337,7 +6354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>45597</v>
       </c>
@@ -6345,14 +6362,14 @@
         <v>15</v>
       </c>
       <c r="C219">
-        <v>8.5000000000000006E-2</v>
+        <v>0.79</v>
       </c>
       <c r="D219">
         <v>1.45</v>
       </c>
       <c r="E219">
         <f t="shared" si="14"/>
-        <v>-1.365</v>
+        <v>-0.65999999999999992</v>
       </c>
       <c r="G219">
         <v>22.5</v>
@@ -6364,7 +6381,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>45597</v>
       </c>
@@ -6387,7 +6404,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>45597</v>
       </c>
@@ -6414,7 +6431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>45597</v>
       </c>
@@ -6441,7 +6458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>45597</v>
       </c>
@@ -6468,7 +6485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>45597</v>
       </c>
@@ -6522,7 +6539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>45597</v>
       </c>
@@ -6549,7 +6566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>45597</v>
       </c>
@@ -6576,7 +6593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>45597</v>
       </c>
@@ -6603,7 +6620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>45597</v>
       </c>
@@ -6631,27 +6648,31 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K213" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}"/>
+  <autoFilter ref="A1:L229" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="6GW5"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46CF97C0-7618-4F8F-82E4-510ABB360005}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -6674,16 +6695,10 @@
         <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6705,21 +6720,13 @@
         <v>1.21</v>
       </c>
       <c r="G2">
-        <f>F2+'screen extent'!B2</f>
-        <v>1.32</v>
+        <v>0.11</v>
       </c>
       <c r="H2">
-        <v>4.554000000000002</v>
-      </c>
-      <c r="I2">
-        <f>H2-F2</f>
-        <v>3.3440000000000021</v>
-      </c>
-      <c r="J2">
         <v>4.2671999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -6741,21 +6748,13 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="G3">
-        <f>F3+'screen extent'!B3</f>
-        <v>0.70499999999999996</v>
+        <v>0.11</v>
       </c>
       <c r="H3">
-        <v>4.0829999999999984</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I18" si="1">H3-F3</f>
-        <v>3.4879999999999987</v>
-      </c>
-      <c r="J3">
         <v>2.1335999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6767,27 +6766,23 @@
       </c>
       <c r="D4">
         <v>0.755</v>
+      </c>
+      <c r="E4">
+        <f>G4-D4</f>
+        <v>-0.95500000000000007</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
         <v>1.165</v>
       </c>
       <c r="G4">
-        <f>F4+'screen extent'!B4</f>
-        <v>0.96500000000000008</v>
+        <v>-0.2</v>
       </c>
       <c r="H4">
-        <v>6.972999999999999</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>5.8079999999999989</v>
-      </c>
-      <c r="J4">
         <v>1.2192000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -6809,21 +6804,13 @@
         <v>1.33</v>
       </c>
       <c r="G5">
-        <f>F5+'screen extent'!B5</f>
-        <v>1.4400000000000002</v>
+        <v>0.11</v>
       </c>
       <c r="H5">
-        <v>4.7550000000000026</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="1"/>
-        <v>3.4250000000000025</v>
-      </c>
-      <c r="J5">
         <v>0.30480000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -6845,21 +6832,13 @@
         <v>0.98000000000000009</v>
       </c>
       <c r="G6">
-        <f>F6+'screen extent'!B6</f>
-        <v>0.98000000000000009</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>3.7040000000000006</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="1"/>
-        <v>2.7240000000000006</v>
-      </c>
-      <c r="J6">
         <v>4.8768000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -6881,21 +6860,13 @@
         <v>1.2550000000000001</v>
       </c>
       <c r="G7">
-        <f>F7+'screen extent'!B7</f>
-        <v>1.2550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>3.6280000000000001</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="1"/>
-        <v>2.3730000000000002</v>
-      </c>
-      <c r="J7">
         <v>7.62</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -6913,21 +6884,13 @@
         <v>1.7799999999999998</v>
       </c>
       <c r="G8">
-        <f>F8+'screen extent'!B8</f>
-        <v>1.9799999999999998</v>
+        <v>0.2</v>
       </c>
       <c r="H8">
-        <v>5.3410000000000011</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="1"/>
-        <v>3.5610000000000013</v>
-      </c>
-      <c r="J8">
         <v>16.806671999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -6944,22 +6907,11 @@
         <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
-      <c r="G9">
-        <f>F9+'screen extent'!B9</f>
-        <v>2.25</v>
-      </c>
       <c r="H9">
-        <v>2.5349999999999966</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>0.28499999999999659</v>
-      </c>
-      <c r="J9">
         <v>0.30480000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6976,22 +6928,11 @@
         <f t="shared" si="0"/>
         <v>2.23</v>
       </c>
-      <c r="G10">
-        <f>F10+'screen extent'!B10</f>
-        <v>2.23</v>
-      </c>
       <c r="H10">
-        <v>11.067</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>8.8369999999999997</v>
-      </c>
-      <c r="J10">
         <v>2.4384000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -7013,21 +6954,13 @@
         <v>1.93</v>
       </c>
       <c r="G11">
-        <f>F11+'screen extent'!B11</f>
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.52199999999999847</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>-1.4080000000000015</v>
-      </c>
-      <c r="J11">
         <v>7.9248000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -7045,21 +6978,13 @@
         <v>2.79</v>
       </c>
       <c r="G12">
-        <f>F12+'screen extent'!B12</f>
-        <v>2.99</v>
+        <v>0.2</v>
       </c>
       <c r="H12">
-        <v>-0.34000000000000341</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>-3.1300000000000034</v>
-      </c>
-      <c r="J12">
         <v>1.524</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7081,21 +7006,13 @@
         <v>4.3049999999999997</v>
       </c>
       <c r="G13">
-        <f>F13+'screen extent'!B13</f>
-        <v>3.4549999999999996</v>
+        <v>-0.85</v>
       </c>
       <c r="H13">
-        <v>-3.3250000000000028</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>-7.6300000000000026</v>
-      </c>
-      <c r="J13">
         <v>7.62</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -7117,21 +7034,13 @@
         <v>0.86999999999999988</v>
       </c>
       <c r="G14">
-        <f>F14+'screen extent'!B14</f>
-        <v>0.98999999999999988</v>
+        <v>0.12</v>
       </c>
       <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="1"/>
-        <v>-0.86999999999999988</v>
-      </c>
-      <c r="J14">
         <v>0.30480000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -7153,21 +7062,13 @@
         <v>1.77</v>
       </c>
       <c r="G15">
-        <f>F15+'screen extent'!B15</f>
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3.4299999999999997</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>1.6599999999999997</v>
-      </c>
-      <c r="J15">
         <v>1.524</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -7189,21 +7090,13 @@
         <v>1.08</v>
       </c>
       <c r="G16">
-        <f>F16+'screen extent'!B16</f>
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>0.3539999999999992</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>-0.72600000000000087</v>
-      </c>
-      <c r="J16">
         <v>4.2671999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -7225,21 +7118,13 @@
         <v>1.25</v>
       </c>
       <c r="G17">
-        <f>F17+'screen extent'!B17</f>
-        <v>1.4</v>
+        <v>0.15</v>
       </c>
       <c r="H17">
-        <v>0.42600000000000193</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>-0.82399999999999807</v>
-      </c>
-      <c r="J17">
         <v>0.3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -7261,17 +7146,9 @@
         <v>1.8699999999999999</v>
       </c>
       <c r="G18">
-        <f>F18+'screen extent'!B18</f>
-        <v>1.8699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>1.267000000000003</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>-0.60299999999999687</v>
-      </c>
-      <c r="J18">
         <v>20</v>
       </c>
     </row>
@@ -7281,6 +7158,157 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{698DE982-E236-43E1-B722-294E070E3A97}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CDFA8B-8EFF-41DF-9628-C4500C1F336E}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7560,7 +7588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD4D3FF-142F-49B1-8302-8B738176724B}">
   <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8202,7 +8230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095E44FE-5111-4C27-A5EF-FDC66449A7D3}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8387,7 +8415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F69B03-BE4F-4A17-B12B-23A1FE1DCC14}">
   <dimension ref="A1:V36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9419,157 +9447,6 @@
     </row>
     <row r="36" spans="17:17" x14ac:dyDescent="0.25">
       <c r="Q36" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{698DE982-E236-43E1-B722-294E070E3A97}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9595,16 +9472,16 @@
         <v>36</v>
       </c>
       <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
         <v>48</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" t="s">
-        <v>50</v>
-      </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -9729,7 +9606,7 @@
         <v>3.41</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
@@ -9738,7 +9615,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -9846,7 +9723,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -9928,7 +9805,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>9</v>

--- a/01_Raw_data/RW.log.xlsx
+++ b/01_Raw_data/RW.log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dissertation\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBE8DBB-1A2F-4BF5-8F40-421FC6AF4B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9454C528-CDE2-4709-AE10-CD72D8DF3032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="6" activeTab="7" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
   </bookViews>
   <sheets>
     <sheet name="log" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="well heightw extension " sheetId="8" r:id="rId6"/>
     <sheet name="well height_raw" sheetId="2" r:id="rId7"/>
     <sheet name="scope elevations" sheetId="11" r:id="rId8"/>
+    <sheet name="scope elevations 04172026" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">log!$A$1:$L$229</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -214,6 +215,21 @@
   </si>
   <si>
     <t>DID NOT PUMP</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>Stream_2</t>
+  </si>
+  <si>
+    <t>GW_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope_2 </t>
   </si>
 </sst>
 </file>
@@ -612,21 +628,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L229"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.140625" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.1328125" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" customWidth="1"/>
+    <col min="10" max="10" width="14.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.40625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45569</v>
       </c>
@@ -688,7 +704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45569</v>
       </c>
@@ -715,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45569</v>
       </c>
@@ -742,7 +758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45569</v>
       </c>
@@ -769,7 +785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45569</v>
       </c>
@@ -800,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45569</v>
       </c>
@@ -827,7 +843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>45569</v>
       </c>
@@ -847,7 +863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>45569</v>
       </c>
@@ -874,7 +890,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>45569</v>
       </c>
@@ -894,7 +910,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45569</v>
       </c>
@@ -922,7 +938,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45569</v>
       </c>
@@ -946,7 +962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>45569</v>
       </c>
@@ -970,7 +986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>45569</v>
       </c>
@@ -998,7 +1014,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>45569</v>
       </c>
@@ -1026,7 +1042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>45569</v>
       </c>
@@ -1054,7 +1070,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>45569</v>
       </c>
@@ -1082,7 +1098,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A18" s="1">
         <v>45687</v>
       </c>
@@ -1113,7 +1129,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A19" s="1">
         <v>45687</v>
       </c>
@@ -1144,7 +1160,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A20" s="1">
         <v>45687</v>
       </c>
@@ -1170,7 +1186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A21" s="1">
         <v>45687</v>
       </c>
@@ -1197,7 +1213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A22" s="1">
         <v>45687</v>
       </c>
@@ -1224,7 +1240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A23" s="1">
         <v>45687</v>
       </c>
@@ -1251,7 +1267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A24" s="1">
         <v>45687</v>
       </c>
@@ -1274,7 +1290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A25" s="1">
         <v>45687</v>
       </c>
@@ -1297,7 +1313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A26" s="1">
         <v>45687</v>
       </c>
@@ -1324,7 +1340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A27" s="1">
         <v>45687</v>
       </c>
@@ -1347,7 +1363,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A28" s="1">
         <v>45687</v>
       </c>
@@ -1378,7 +1394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A29" s="1">
         <v>45687</v>
       </c>
@@ -1405,7 +1421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A30" s="1">
         <v>45687</v>
       </c>
@@ -1432,7 +1448,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A31" s="1">
         <v>45687</v>
       </c>
@@ -1463,7 +1479,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A32" s="1">
         <v>45687</v>
       </c>
@@ -1494,7 +1510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A33" s="1">
         <v>45687</v>
       </c>
@@ -1525,7 +1541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A34" s="1">
         <v>45687</v>
       </c>
@@ -1556,7 +1572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A35" s="1">
         <v>45687</v>
       </c>
@@ -1583,7 +1599,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A36" s="1">
         <v>45728</v>
       </c>
@@ -1614,7 +1630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A37" s="1">
         <v>45728</v>
       </c>
@@ -1644,7 +1660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A38" s="1">
         <v>45728</v>
       </c>
@@ -1670,7 +1686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A39" s="1">
         <v>45728</v>
       </c>
@@ -1697,7 +1713,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A40" s="1">
         <v>45728</v>
       </c>
@@ -1724,7 +1740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A41" s="1">
         <v>45728</v>
       </c>
@@ -1751,7 +1767,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A42" s="1">
         <v>45728</v>
       </c>
@@ -1771,7 +1787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A43" s="1">
         <v>45728</v>
       </c>
@@ -1797,7 +1813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A44" s="1">
         <v>45728</v>
       </c>
@@ -1824,7 +1840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A45" s="1">
         <v>45728</v>
       </c>
@@ -1850,7 +1866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A46" s="1">
         <v>45728</v>
       </c>
@@ -1881,7 +1897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A47" s="1">
         <v>45728</v>
       </c>
@@ -1908,7 +1924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A48" s="1">
         <v>45728</v>
       </c>
@@ -1935,7 +1951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A49" s="1">
         <v>45728</v>
       </c>
@@ -1966,7 +1982,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A50" s="1">
         <v>45728</v>
       </c>
@@ -1997,7 +2013,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A51" s="1">
         <v>45728</v>
       </c>
@@ -2028,7 +2044,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A52" s="1">
         <v>45728</v>
       </c>
@@ -2059,7 +2075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A53" s="1">
         <v>45728</v>
       </c>
@@ -2086,7 +2102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A54" s="1">
         <v>45764</v>
       </c>
@@ -2114,7 +2130,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A55" s="1">
         <v>45764</v>
       </c>
@@ -2145,7 +2161,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A56" s="1">
         <v>45764</v>
       </c>
@@ -2172,7 +2188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A57" s="1">
         <v>45764</v>
       </c>
@@ -2199,7 +2215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A58" s="1">
         <v>45764</v>
       </c>
@@ -2230,7 +2246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A59" s="1">
         <v>45764</v>
       </c>
@@ -2257,7 +2273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A60" s="1">
         <v>45764</v>
       </c>
@@ -2271,7 +2287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A61" s="1">
         <v>45764</v>
       </c>
@@ -2298,7 +2314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A62" s="1">
         <v>45764</v>
       </c>
@@ -2325,7 +2341,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A63" s="1">
         <v>45764</v>
       </c>
@@ -2352,7 +2368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A64" s="1">
         <v>45764</v>
       </c>
@@ -2383,7 +2399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A65" s="1">
         <v>45764</v>
       </c>
@@ -2410,7 +2426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A66" s="1">
         <v>45764</v>
       </c>
@@ -2437,7 +2453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A67" s="1">
         <v>45764</v>
       </c>
@@ -2465,7 +2481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A68" s="1">
         <v>45764</v>
       </c>
@@ -2493,7 +2509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A69" s="1">
         <v>45764</v>
       </c>
@@ -2521,7 +2537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A70" s="1">
         <v>45764</v>
       </c>
@@ -2549,7 +2565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A71" s="1">
         <v>45764</v>
       </c>
@@ -2566,7 +2582,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A72" s="1">
         <v>45400</v>
       </c>
@@ -2594,7 +2610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A73" s="1">
         <v>45400</v>
       </c>
@@ -2622,7 +2638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A74" s="1">
         <v>45400</v>
       </c>
@@ -2646,7 +2662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A75" s="1">
         <v>45400</v>
       </c>
@@ -2670,7 +2686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A76" s="1">
         <v>45400</v>
       </c>
@@ -2698,7 +2714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A77" s="1">
         <v>45400</v>
       </c>
@@ -2719,7 +2735,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A78" s="1">
         <v>45400</v>
       </c>
@@ -2743,7 +2759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A79" s="1">
         <v>45400</v>
       </c>
@@ -2766,7 +2782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A80" s="1">
         <v>45400</v>
       </c>
@@ -2794,7 +2810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A81" s="1">
         <v>45400</v>
       </c>
@@ -2818,7 +2834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A82" s="1">
         <v>45400</v>
       </c>
@@ -2839,7 +2855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A83" s="1">
         <v>45400</v>
       </c>
@@ -2867,7 +2883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A84" s="1">
         <v>45400</v>
       </c>
@@ -2895,7 +2911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A85" s="1">
         <v>45400</v>
       </c>
@@ -2923,7 +2939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A86" s="1">
         <v>45400</v>
       </c>
@@ -2951,7 +2967,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A87" s="1">
         <v>45463</v>
       </c>
@@ -2977,7 +2993,7 @@
       </c>
       <c r="K87" s="3"/>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A88" s="1">
         <v>45457</v>
       </c>
@@ -3002,7 +3018,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A89" s="1">
         <v>45462</v>
       </c>
@@ -3030,7 +3046,7 @@
       </c>
       <c r="K89" s="3"/>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A90" s="1">
         <v>45463</v>
       </c>
@@ -3054,7 +3070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A91" s="1">
         <v>45462</v>
       </c>
@@ -3080,7 +3096,7 @@
       </c>
       <c r="K91" s="3"/>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A92" s="1">
         <v>45463</v>
       </c>
@@ -3101,7 +3117,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A93" s="1">
         <v>45462</v>
       </c>
@@ -3109,7 +3125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A94" s="1">
         <v>45463</v>
       </c>
@@ -3133,7 +3149,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A95" s="1">
         <v>45463</v>
       </c>
@@ -3157,7 +3173,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A96" s="1">
         <v>45463</v>
       </c>
@@ -3178,7 +3194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A97" s="1">
         <v>45463</v>
       </c>
@@ -3199,7 +3215,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A98" s="1">
         <v>45463</v>
       </c>
@@ -3224,7 +3240,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A99" s="1">
         <v>45463</v>
       </c>
@@ -3249,7 +3265,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A100" s="1">
         <v>45463</v>
       </c>
@@ -3274,7 +3290,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A101" s="1">
         <v>45484</v>
       </c>
@@ -3302,7 +3318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A102" s="1">
         <v>45484</v>
       </c>
@@ -3329,7 +3345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A103" s="1">
         <v>45484</v>
       </c>
@@ -3352,7 +3368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A104" s="1">
         <v>45484</v>
       </c>
@@ -3378,7 +3394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A105" s="1">
         <v>45484</v>
       </c>
@@ -3405,7 +3421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A106" s="1">
         <v>45484</v>
       </c>
@@ -3432,7 +3448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A107" s="1">
         <v>45484</v>
       </c>
@@ -3452,7 +3468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A108" s="1">
         <v>45484</v>
       </c>
@@ -3479,7 +3495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A109" s="1">
         <v>45484</v>
       </c>
@@ -3506,7 +3522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A110" s="1">
         <v>45484</v>
       </c>
@@ -3530,7 +3546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A111" s="1">
         <v>45484</v>
       </c>
@@ -3547,7 +3563,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A112" s="1">
         <v>45484</v>
       </c>
@@ -3574,7 +3590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A113" s="1">
         <v>45484</v>
       </c>
@@ -3601,7 +3617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A114" s="1">
         <v>45484</v>
       </c>
@@ -3619,7 +3635,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A115" s="1">
         <v>45635</v>
       </c>
@@ -3650,7 +3666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A116" s="1">
         <v>45635</v>
       </c>
@@ -3680,7 +3696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A117" s="1">
         <v>45635</v>
       </c>
@@ -3707,7 +3723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A118" s="1">
         <v>45635</v>
       </c>
@@ -3734,7 +3750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A119" s="1">
         <v>45635</v>
       </c>
@@ -3765,7 +3781,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A120" s="1">
         <v>45635</v>
       </c>
@@ -3792,7 +3808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A121" s="1">
         <v>45635</v>
       </c>
@@ -3813,7 +3829,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A122" s="1">
         <v>45635</v>
       </c>
@@ -3840,7 +3856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A123" s="1">
         <v>45635</v>
       </c>
@@ -3867,7 +3883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A124" s="1">
         <v>45635</v>
       </c>
@@ -3894,7 +3910,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A125" s="1">
         <v>45635</v>
       </c>
@@ -3925,7 +3941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A126" s="1">
         <v>45635</v>
       </c>
@@ -3952,7 +3968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A127" s="1">
         <v>45635</v>
       </c>
@@ -3979,7 +3995,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A128" s="1">
         <v>45635</v>
       </c>
@@ -4010,7 +4026,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A129" s="1">
         <v>45635</v>
       </c>
@@ -4041,7 +4057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A130" s="1">
         <v>45635</v>
       </c>
@@ -4072,7 +4088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A131" s="1">
         <v>45635</v>
       </c>
@@ -4103,7 +4119,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A132" s="1">
         <v>45635</v>
       </c>
@@ -4130,7 +4146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A133" s="1">
         <v>45667</v>
       </c>
@@ -4155,7 +4171,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A134" s="1">
         <v>45667</v>
       </c>
@@ -4186,7 +4202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A135" s="1">
         <v>45667</v>
       </c>
@@ -4213,7 +4229,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A136" s="1">
         <v>45667</v>
       </c>
@@ -4240,7 +4256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A137" s="1">
         <v>45667</v>
       </c>
@@ -4271,7 +4287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A138" s="1">
         <v>45667</v>
       </c>
@@ -4298,7 +4314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A139" s="1">
         <v>45667</v>
       </c>
@@ -4322,7 +4338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A140" s="1">
         <v>45667</v>
       </c>
@@ -4343,7 +4359,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A141" s="1">
         <v>45667</v>
       </c>
@@ -4370,7 +4386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A142" s="1">
         <v>45667</v>
       </c>
@@ -4397,7 +4413,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A143" s="1">
         <v>45667</v>
       </c>
@@ -4428,7 +4444,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A144" s="1">
         <v>45667</v>
       </c>
@@ -4455,7 +4471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A145" s="1">
         <v>45667</v>
       </c>
@@ -4472,7 +4488,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A146" s="1">
         <v>45667</v>
       </c>
@@ -4503,7 +4519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A147" s="1">
         <v>45667</v>
       </c>
@@ -4534,7 +4550,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A148" s="1">
         <v>45667</v>
       </c>
@@ -4565,7 +4581,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A149" s="1">
         <v>45667</v>
       </c>
@@ -4599,7 +4615,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A150" s="1">
         <v>45667</v>
       </c>
@@ -4626,7 +4642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A151" s="1">
         <v>45502</v>
       </c>
@@ -4654,7 +4670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A152" s="1">
         <v>45502</v>
       </c>
@@ -4681,7 +4697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A153" s="1">
         <v>45502</v>
       </c>
@@ -4704,7 +4720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A154" s="1">
         <v>45502</v>
       </c>
@@ -4731,7 +4747,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A155" s="1">
         <v>45502</v>
       </c>
@@ -4758,7 +4774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A156" s="1">
         <v>45502</v>
       </c>
@@ -4785,7 +4801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A157" s="1">
         <v>45502</v>
       </c>
@@ -4812,7 +4828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A158" s="1">
         <v>45502</v>
       </c>
@@ -4839,7 +4855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A159" s="1">
         <v>45502</v>
       </c>
@@ -4870,7 +4886,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A160" s="1">
         <v>45502</v>
       </c>
@@ -4897,7 +4913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A161" s="1">
         <v>45502</v>
       </c>
@@ -4911,7 +4927,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A162" s="1">
         <v>45502</v>
       </c>
@@ -4942,7 +4958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A163" s="1">
         <v>45502</v>
       </c>
@@ -4973,7 +4989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A164" s="1">
         <v>45502</v>
       </c>
@@ -5004,7 +5020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A165" s="1">
         <v>45502</v>
       </c>
@@ -5029,7 +5045,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A166" s="1">
         <v>45534</v>
       </c>
@@ -5056,7 +5072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A167" s="1">
         <v>45534</v>
       </c>
@@ -5083,7 +5099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A168" s="1">
         <v>45534</v>
       </c>
@@ -5110,7 +5126,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A169" s="1">
         <v>45534</v>
       </c>
@@ -5137,7 +5153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A170" s="1">
         <v>45534</v>
       </c>
@@ -5168,7 +5184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A171" s="1">
         <v>45534</v>
       </c>
@@ -5188,7 +5204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A172" s="1">
         <v>45534</v>
       </c>
@@ -5205,7 +5221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A173" s="1">
         <v>45534</v>
       </c>
@@ -5225,7 +5241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A174" s="1">
         <v>45534</v>
       </c>
@@ -5248,7 +5264,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A175" s="1">
         <v>45534</v>
       </c>
@@ -5275,7 +5291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A176" s="1">
         <v>45534</v>
       </c>
@@ -5298,7 +5314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A177" s="1">
         <v>45534</v>
       </c>
@@ -5322,7 +5338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A178" s="1">
         <v>45534</v>
       </c>
@@ -5347,7 +5363,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A179" s="1">
         <v>45534</v>
       </c>
@@ -5371,7 +5387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A180" s="1">
         <v>45534</v>
       </c>
@@ -5395,7 +5411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A181" s="1">
         <v>45534</v>
       </c>
@@ -5414,7 +5430,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A182" s="1">
         <v>45442</v>
       </c>
@@ -5439,7 +5455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A183" s="1">
         <v>45442</v>
       </c>
@@ -5467,7 +5483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A184" s="1">
         <v>45442</v>
       </c>
@@ -5491,7 +5507,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A185" s="1">
         <v>45442</v>
       </c>
@@ -5515,7 +5531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A186" s="1">
         <v>45442</v>
       </c>
@@ -5543,7 +5559,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A187" s="1">
         <v>45442</v>
       </c>
@@ -5567,7 +5583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A188" s="1">
         <v>45442</v>
       </c>
@@ -5582,7 +5598,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A189" s="1">
         <v>45442</v>
       </c>
@@ -5594,7 +5610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A190" s="1">
         <v>45442</v>
       </c>
@@ -5619,7 +5635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A191" s="1">
         <v>45442</v>
       </c>
@@ -5631,7 +5647,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A192" s="1">
         <v>45442</v>
       </c>
@@ -5646,7 +5662,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A193" s="1">
         <v>45442</v>
       </c>
@@ -5674,7 +5690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A194" s="1">
         <v>45442</v>
       </c>
@@ -5699,7 +5715,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A195" s="1">
         <v>45442</v>
       </c>
@@ -5727,7 +5743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A196" s="1">
         <v>45442</v>
       </c>
@@ -5755,7 +5771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A197" s="1">
         <v>45940</v>
       </c>
@@ -5786,7 +5802,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A198" s="1">
         <v>45940</v>
       </c>
@@ -5820,7 +5836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A199" s="1">
         <v>45940</v>
       </c>
@@ -5847,7 +5863,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A200" s="1">
         <v>45940</v>
       </c>
@@ -5877,7 +5893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A201" s="1">
         <v>45940</v>
       </c>
@@ -5911,7 +5927,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A202" s="1">
         <v>45940</v>
       </c>
@@ -5941,7 +5957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A203" s="1">
         <v>45940</v>
       </c>
@@ -5971,7 +5987,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A204" s="1">
         <v>45940</v>
       </c>
@@ -5992,7 +6008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A205" s="1">
         <v>45940</v>
       </c>
@@ -6013,7 +6029,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A206" s="1">
         <v>45940</v>
       </c>
@@ -6040,7 +6056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A207" s="1">
         <v>45940</v>
       </c>
@@ -6070,7 +6086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A208" s="1">
         <v>45940</v>
       </c>
@@ -6091,7 +6107,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A209" s="1">
         <v>45940</v>
       </c>
@@ -6116,7 +6132,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A210" s="1">
         <v>45940</v>
       </c>
@@ -6150,7 +6166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A211" s="1">
         <v>45940</v>
       </c>
@@ -6164,7 +6180,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A212" s="1">
         <v>45940</v>
       </c>
@@ -6189,7 +6205,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A213" s="1">
         <v>45940</v>
       </c>
@@ -6219,7 +6235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A214" s="1">
         <v>45597</v>
       </c>
@@ -6246,7 +6262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A215" s="1">
         <v>45597</v>
       </c>
@@ -6273,7 +6289,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A216" s="1">
         <v>45597</v>
       </c>
@@ -6300,7 +6316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A217" s="1">
         <v>45597</v>
       </c>
@@ -6327,7 +6343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A218" s="1">
         <v>45597</v>
       </c>
@@ -6354,7 +6370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A219" s="1">
         <v>45597</v>
       </c>
@@ -6381,7 +6397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A220" s="1">
         <v>45597</v>
       </c>
@@ -6404,7 +6420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A221" s="1">
         <v>45597</v>
       </c>
@@ -6431,7 +6447,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A222" s="1">
         <v>45597</v>
       </c>
@@ -6458,7 +6474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A223" s="1">
         <v>45597</v>
       </c>
@@ -6485,7 +6501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A224" s="1">
         <v>45597</v>
       </c>
@@ -6512,7 +6528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A225" s="1">
         <v>45597</v>
       </c>
@@ -6539,7 +6555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A226" s="1">
         <v>45597</v>
       </c>
@@ -6566,7 +6582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A227" s="1">
         <v>45597</v>
       </c>
@@ -6593,7 +6609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A228" s="1">
         <v>45597</v>
       </c>
@@ -6620,7 +6636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A229" s="1">
         <v>45597</v>
       </c>
@@ -6662,17 +6678,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46CF97C0-7618-4F8F-82E4-510ABB360005}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -6698,7 +6714,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6726,7 +6742,7 @@
         <v>4.2671999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -6754,7 +6770,7 @@
         <v>2.1335999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6782,7 +6798,7 @@
         <v>1.2192000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -6810,7 +6826,7 @@
         <v>0.30480000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -6838,7 +6854,7 @@
         <v>4.8768000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -6866,7 +6882,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -6890,7 +6906,7 @@
         <v>16.806671999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -6911,7 +6927,7 @@
         <v>0.30480000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6932,7 +6948,7 @@
         <v>2.4384000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -6960,7 +6976,7 @@
         <v>7.9248000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -6984,7 +7000,7 @@
         <v>1.524</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7012,7 +7028,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -7040,7 +7056,7 @@
         <v>0.30480000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -7068,7 +7084,7 @@
         <v>1.524</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -7096,7 +7112,7 @@
         <v>4.2671999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -7124,7 +7140,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -7160,12 +7176,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{698DE982-E236-43E1-B722-294E070E3A97}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.40625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -7173,7 +7189,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7181,7 +7197,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -7189,7 +7205,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7197,7 +7213,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -7205,7 +7221,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -7213,7 +7229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -7221,7 +7237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -7229,17 +7245,17 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -7247,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -7255,7 +7271,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7263,7 +7279,7 @@
         <v>-0.85</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -7271,7 +7287,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -7279,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -7287,7 +7303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -7295,7 +7311,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -7311,13 +7327,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CDFA8B-8EFF-41DF-9628-C4500C1F336E}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.40625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -7328,7 +7344,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7343,7 +7359,7 @@
         <v>4.554000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -7358,7 +7374,7 @@
         <v>4.0829999999999984</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7373,7 +7389,7 @@
         <v>6.972999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -7388,7 +7404,7 @@
         <v>4.7550000000000026</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -7403,7 +7419,7 @@
         <v>3.7040000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -7418,7 +7434,7 @@
         <v>3.6280000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -7433,7 +7449,7 @@
         <v>5.3410000000000011</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -7448,7 +7464,7 @@
         <v>2.5349999999999966</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -7463,7 +7479,7 @@
         <v>11.067</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -7478,7 +7494,7 @@
         <v>0.52199999999999847</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -7493,7 +7509,7 @@
         <v>-0.34000000000000341</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7508,7 +7524,7 @@
         <v>-3.3250000000000028</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -7523,7 +7539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -7538,7 +7554,7 @@
         <v>3.4299999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -7553,7 +7569,7 @@
         <v>0.3539999999999992</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -7568,7 +7584,7 @@
         <v>0.42600000000000193</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -7591,15 +7607,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD4D3FF-142F-49B1-8302-8B738176724B}">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.40625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A1" s="1">
         <v>45442</v>
       </c>
@@ -7637,7 +7653,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45442</v>
       </c>
@@ -7675,7 +7691,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45442</v>
       </c>
@@ -7710,7 +7726,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45442</v>
       </c>
@@ -7751,7 +7767,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45442</v>
       </c>
@@ -7786,7 +7802,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45442</v>
       </c>
@@ -7827,7 +7843,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45442</v>
       </c>
@@ -7859,7 +7875,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>45442</v>
       </c>
@@ -7897,7 +7913,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>45442</v>
       </c>
@@ -7938,7 +7954,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>45442</v>
       </c>
@@ -7976,7 +7992,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45442</v>
       </c>
@@ -8014,7 +8030,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45442</v>
       </c>
@@ -8055,7 +8071,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>45442</v>
       </c>
@@ -8096,7 +8112,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>45442</v>
       </c>
@@ -8134,7 +8150,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>45442</v>
       </c>
@@ -8172,7 +8188,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>45442</v>
       </c>
@@ -8214,7 +8230,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="17" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="15:17" x14ac:dyDescent="0.75">
       <c r="O17" t="s">
         <v>29</v>
       </c>
@@ -8233,12 +8249,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095E44FE-5111-4C27-A5EF-FDC66449A7D3}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1">
         <v>45940</v>
       </c>
@@ -8249,7 +8265,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45940</v>
       </c>
@@ -8260,7 +8276,7 @@
         <v>143.19999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45940</v>
       </c>
@@ -8268,7 +8284,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45940</v>
       </c>
@@ -8279,7 +8295,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45940</v>
       </c>
@@ -8290,7 +8306,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45940</v>
       </c>
@@ -8301,7 +8317,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45940</v>
       </c>
@@ -8309,7 +8325,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>45940</v>
       </c>
@@ -8317,7 +8333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>45940</v>
       </c>
@@ -8325,7 +8341,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>45940</v>
       </c>
@@ -8336,7 +8352,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45940</v>
       </c>
@@ -8344,7 +8360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45940</v>
       </c>
@@ -8355,7 +8371,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>45940</v>
       </c>
@@ -8366,7 +8382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>45940</v>
       </c>
@@ -8377,7 +8393,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>45940</v>
       </c>
@@ -8388,7 +8404,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>45940</v>
       </c>
@@ -8399,7 +8415,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>45940</v>
       </c>
@@ -8418,13 +8434,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F69B03-BE4F-4A17-B12B-23A1FE1DCC14}">
   <dimension ref="A1:V36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="14" max="14" width="9.140625" style="5"/>
+    <col min="14" max="14" width="9.1328125" style="5"/>
     <col min="21" max="21" width="10" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A1" s="1">
         <v>45635</v>
       </c>
@@ -8478,7 +8494,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45635</v>
       </c>
@@ -8534,7 +8550,7 @@
         <v>0.41499999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45635</v>
       </c>
@@ -8590,7 +8606,7 @@
         <v>0.755</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45635</v>
       </c>
@@ -8646,7 +8662,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45635</v>
       </c>
@@ -8702,7 +8718,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45635</v>
       </c>
@@ -8758,7 +8774,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45635</v>
       </c>
@@ -8797,7 +8813,7 @@
       </c>
       <c r="U7"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>45635</v>
       </c>
@@ -8846,7 +8862,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>45635</v>
       </c>
@@ -8902,7 +8918,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>45635</v>
       </c>
@@ -8958,7 +8974,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45635</v>
       </c>
@@ -9014,7 +9030,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45635</v>
       </c>
@@ -9070,7 +9086,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>45635</v>
       </c>
@@ -9123,7 +9139,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>45635</v>
       </c>
@@ -9179,7 +9195,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>45635</v>
       </c>
@@ -9235,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>45635</v>
       </c>
@@ -9291,7 +9307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>45635</v>
       </c>
@@ -9347,7 +9363,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.75">
       <c r="A18" s="1">
         <v>45635</v>
       </c>
@@ -9394,58 +9410,58 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q21" s="5"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q22" s="5"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q23" s="5"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q24" s="5"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q26" s="5"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q27" s="5"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q28" s="5"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q29" s="5"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q30" s="5"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q31" s="5"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.75">
       <c r="Q32" s="5"/>
     </row>
-    <row r="33" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="17:17" x14ac:dyDescent="0.75">
       <c r="Q33" s="5"/>
     </row>
-    <row r="34" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="17:17" x14ac:dyDescent="0.75">
       <c r="Q34" s="5"/>
     </row>
-    <row r="35" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="17:17" x14ac:dyDescent="0.75">
       <c r="Q35" s="5"/>
     </row>
-    <row r="36" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="17:17" x14ac:dyDescent="0.75">
       <c r="Q36" s="5"/>
     </row>
   </sheetData>
@@ -9456,15 +9472,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E402A7-5FED-4C94-AF89-3A3789BD6BB3}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9484,7 +9500,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -9502,7 +9518,7 @@
         <v>1.8399999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9516,11 +9532,11 @@
         <v>5.24</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F9" si="0">$D$9-D3</f>
+        <f>$D$9-D3</f>
         <v>0.9399999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -9534,11 +9550,11 @@
         <v>5.8</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F3:F9" si="0">$D$9-D4</f>
         <v>0.37999999999999989</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9556,7 +9572,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9574,7 +9590,7 @@
         <v>0.13999999999999968</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9592,7 +9608,7 @@
         <v>2.4699999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -9613,7 +9629,7 @@
         <v>2.7699999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -9631,7 +9647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -9649,7 +9665,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -9667,7 +9683,7 @@
         <v>1.1999999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -9685,7 +9701,7 @@
         <v>3.4899999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -9703,7 +9719,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -9721,7 +9737,7 @@
         <v>4.2799999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -9739,7 +9755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -9755,7 +9771,7 @@
         <v>1.4399999999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -9771,7 +9787,7 @@
         <v>2.2249999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -9787,7 +9803,7 @@
         <v>2.0350000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -9803,7 +9819,7 @@
         <v>2.4649999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -9819,7 +9835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -9833,6 +9849,209 @@
       <c r="F21">
         <f>$D$20-D21</f>
         <v>2.46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022C6BC1-EA40-4831-89E2-8DEF82D847DC}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="D2">
+        <f>$C$3-C2</f>
+        <v>4.2600000000000007</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>3.94</v>
+      </c>
+      <c r="H2">
+        <f>G2-$G$4</f>
+        <v>0.69999999999999973</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>8.4</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D9" si="0">$C$3-C3</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>4.34</v>
+      </c>
+      <c r="H3">
+        <f>G3-$G$4</f>
+        <v>1.0999999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>6.58</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>1.8200000000000003</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>3.24</v>
+      </c>
+      <c r="H4">
+        <f>G4-$G$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>4.08</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>4.32</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1.72</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>6.6800000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <f>C7+H3</f>
+        <v>5.5</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>2.9000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <f>C7+H2</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000007</v>
       </c>
     </row>
   </sheetData>

--- a/01_Raw_data/RW.log.xlsx
+++ b/01_Raw_data/RW.log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dissertation\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9454C528-CDE2-4709-AE10-CD72D8DF3032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE545C8-3F5A-468A-A23B-4E18DC035BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="6" activeTab="7" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="6" activeTab="8" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
   </bookViews>
   <sheets>
     <sheet name="log" sheetId="1" r:id="rId1"/>
@@ -863,7 +863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>45569</v>
       </c>
@@ -962,7 +962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>45569</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A26" s="1">
         <v>45687</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A30" s="1">
         <v>45687</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A44" s="1">
         <v>45728</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A48" s="1">
         <v>45728</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A62" s="1">
         <v>45764</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A66" s="1">
         <v>45764</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A78" s="1">
         <v>45400</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
       <c r="A82" s="1">
         <v>45400</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A94" s="1">
         <v>45463</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A97" s="1">
         <v>45463</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A110" s="1">
         <v>45484</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A123" s="1">
         <v>45635</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A127" s="1">
         <v>45635</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A141" s="1">
         <v>45667</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
       <c r="A145" s="1">
         <v>45667</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A157" s="1">
         <v>45502</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A161" s="1">
         <v>45502</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A173" s="1">
         <v>45534</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A177" s="1">
         <v>45534</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A188" s="1">
         <v>45442</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A192" s="1">
         <v>45442</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A204" s="1">
         <v>45940</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A208" s="1">
         <v>45940</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A221" s="1">
         <v>45597</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
       <c r="A225" s="1">
         <v>45597</v>
       </c>
@@ -6667,7 +6667,7 @@
   <autoFilter ref="A1:L229" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}">
     <filterColumn colId="1">
       <filters>
-        <filter val="6GW5"/>
+        <filter val="6GW1"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9471,7 +9471,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E402A7-5FED-4C94-AF89-3A3789BD6BB3}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="3" max="3" width="14.1328125" bestFit="1" customWidth="1"/>
@@ -9480,7 +9480,7 @@
     <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>1.8399999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>0.9399999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -9550,11 +9550,11 @@
         <v>5.8</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F3:F9" si="0">$D$9-D4</f>
+        <f t="shared" ref="F4:F9" si="0">$D$9-D4</f>
         <v>0.37999999999999989</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>0.13999999999999968</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>2.4699999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>2.7699999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>1.1999999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>3.4899999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -9719,7 +9719,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>4.2799999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -9755,7 +9755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -9769,6 +9769,10 @@
       <c r="F16">
         <f t="shared" ref="F16:F19" si="2">$D$20-D16</f>
         <v>1.4399999999999995</v>
+      </c>
+      <c r="H16">
+        <f>D15-D10</f>
+        <v>1.96</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.75">
@@ -9858,8 +9862,11 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022C6BC1-EA40-4831-89E2-8DEF82D847DC}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
@@ -10054,6 +10061,138 @@
         <v>3.3000000000000007</v>
       </c>
     </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>2.4500000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A19" s="3">
+        <v>6</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>6.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/01_Raw_data/RW.log.xlsx
+++ b/01_Raw_data/RW.log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dissertation\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE545C8-3F5A-468A-A23B-4E18DC035BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452A8297-69D4-4B39-AE42-CA42E4C9C768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="6" activeTab="8" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{C78ACADB-B7B5-4EBE-89C6-A41D88DD91B0}"/>
   </bookViews>
   <sheets>
     <sheet name="log" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="63">
   <si>
     <t>Date</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t xml:space="preserve">Scope_2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry then refilled; refilled to shallow for YSI reading </t>
+  </si>
+  <si>
+    <t>refilled</t>
   </si>
 </sst>
 </file>
@@ -626,8 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L229"/>
+  <dimension ref="A1:L245"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
@@ -677,7 +682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>45569</v>
       </c>
@@ -704,7 +709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>45569</v>
       </c>
@@ -731,7 +736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>45569</v>
       </c>
@@ -758,7 +763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45569</v>
       </c>
@@ -785,7 +790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45569</v>
       </c>
@@ -816,7 +821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45569</v>
       </c>
@@ -843,7 +848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>45569</v>
       </c>
@@ -890,7 +895,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A10" s="1">
         <v>45569</v>
       </c>
@@ -910,7 +915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45569</v>
       </c>
@@ -938,7 +943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45569</v>
       </c>
@@ -962,7 +967,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A13" s="1">
         <v>45569</v>
       </c>
@@ -986,7 +991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A14" s="1">
         <v>45569</v>
       </c>
@@ -1014,7 +1019,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A15" s="1">
         <v>45569</v>
       </c>
@@ -1042,7 +1047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A16" s="1">
         <v>45569</v>
       </c>
@@ -1070,7 +1075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A17" s="1">
         <v>45569</v>
       </c>
@@ -1098,7 +1103,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A18" s="1">
         <v>45687</v>
       </c>
@@ -1129,7 +1134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A19" s="1">
         <v>45687</v>
       </c>
@@ -1160,7 +1165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A20" s="1">
         <v>45687</v>
       </c>
@@ -1186,7 +1191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A21" s="1">
         <v>45687</v>
       </c>
@@ -1213,7 +1218,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A22" s="1">
         <v>45687</v>
       </c>
@@ -1240,7 +1245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A23" s="1">
         <v>45687</v>
       </c>
@@ -1267,7 +1272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A24" s="1">
         <v>45687</v>
       </c>
@@ -1290,7 +1295,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A25" s="1">
         <v>45687</v>
       </c>
@@ -1340,7 +1345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A27" s="1">
         <v>45687</v>
       </c>
@@ -1363,7 +1368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A28" s="1">
         <v>45687</v>
       </c>
@@ -1394,7 +1399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A29" s="1">
         <v>45687</v>
       </c>
@@ -1421,7 +1426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A30" s="1">
         <v>45687</v>
       </c>
@@ -1448,7 +1453,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A31" s="1">
         <v>45687</v>
       </c>
@@ -1479,7 +1484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A32" s="1">
         <v>45687</v>
       </c>
@@ -1510,7 +1515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A33" s="1">
         <v>45687</v>
       </c>
@@ -1541,7 +1546,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A34" s="1">
         <v>45687</v>
       </c>
@@ -1572,7 +1577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A35" s="1">
         <v>45687</v>
       </c>
@@ -1599,7 +1604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A36" s="1">
         <v>45728</v>
       </c>
@@ -1630,7 +1635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A37" s="1">
         <v>45728</v>
       </c>
@@ -1660,7 +1665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A38" s="1">
         <v>45728</v>
       </c>
@@ -1686,7 +1691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A39" s="1">
         <v>45728</v>
       </c>
@@ -1713,7 +1718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A40" s="1">
         <v>45728</v>
       </c>
@@ -1740,7 +1745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A41" s="1">
         <v>45728</v>
       </c>
@@ -1767,7 +1772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A42" s="1">
         <v>45728</v>
       </c>
@@ -1787,7 +1792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A43" s="1">
         <v>45728</v>
       </c>
@@ -1840,7 +1845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A45" s="1">
         <v>45728</v>
       </c>
@@ -1866,7 +1871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A46" s="1">
         <v>45728</v>
       </c>
@@ -1897,7 +1902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A47" s="1">
         <v>45728</v>
       </c>
@@ -1924,7 +1929,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A48" s="1">
         <v>45728</v>
       </c>
@@ -1951,7 +1956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A49" s="1">
         <v>45728</v>
       </c>
@@ -1982,7 +1987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A50" s="1">
         <v>45728</v>
       </c>
@@ -2013,7 +2018,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A51" s="1">
         <v>45728</v>
       </c>
@@ -2044,7 +2049,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A52" s="1">
         <v>45728</v>
       </c>
@@ -2075,7 +2080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A53" s="1">
         <v>45728</v>
       </c>
@@ -2102,7 +2107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A54" s="1">
         <v>45764</v>
       </c>
@@ -2130,7 +2135,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A55" s="1">
         <v>45764</v>
       </c>
@@ -2161,7 +2166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A56" s="1">
         <v>45764</v>
       </c>
@@ -2188,7 +2193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A57" s="1">
         <v>45764</v>
       </c>
@@ -2215,7 +2220,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A58" s="1">
         <v>45764</v>
       </c>
@@ -2246,7 +2251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A59" s="1">
         <v>45764</v>
       </c>
@@ -2273,7 +2278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A60" s="1">
         <v>45764</v>
       </c>
@@ -2287,7 +2292,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A61" s="1">
         <v>45764</v>
       </c>
@@ -2341,7 +2346,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A63" s="1">
         <v>45764</v>
       </c>
@@ -2368,7 +2373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A64" s="1">
         <v>45764</v>
       </c>
@@ -2399,7 +2404,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A65" s="1">
         <v>45764</v>
       </c>
@@ -2426,7 +2431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A66" s="1">
         <v>45764</v>
       </c>
@@ -2453,7 +2458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A67" s="1">
         <v>45764</v>
       </c>
@@ -2481,7 +2486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A68" s="1">
         <v>45764</v>
       </c>
@@ -2509,7 +2514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A69" s="1">
         <v>45764</v>
       </c>
@@ -2537,7 +2542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A70" s="1">
         <v>45764</v>
       </c>
@@ -2565,7 +2570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A71" s="1">
         <v>45764</v>
       </c>
@@ -2582,7 +2587,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A72" s="1">
         <v>45400</v>
       </c>
@@ -2610,7 +2615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A73" s="1">
         <v>45400</v>
       </c>
@@ -2638,7 +2643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A74" s="1">
         <v>45400</v>
       </c>
@@ -2662,7 +2667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A75" s="1">
         <v>45400</v>
       </c>
@@ -2686,7 +2691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A76" s="1">
         <v>45400</v>
       </c>
@@ -2714,7 +2719,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A77" s="1">
         <v>45400</v>
       </c>
@@ -2759,7 +2764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A79" s="1">
         <v>45400</v>
       </c>
@@ -2782,7 +2787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A80" s="1">
         <v>45400</v>
       </c>
@@ -2810,7 +2815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A81" s="1">
         <v>45400</v>
       </c>
@@ -2834,7 +2839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A82" s="1">
         <v>45400</v>
       </c>
@@ -2855,7 +2860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A83" s="1">
         <v>45400</v>
       </c>
@@ -2883,7 +2888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A84" s="1">
         <v>45400</v>
       </c>
@@ -2911,7 +2916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A85" s="1">
         <v>45400</v>
       </c>
@@ -2939,7 +2944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A86" s="1">
         <v>45400</v>
       </c>
@@ -2967,7 +2972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A87" s="1">
         <v>45463</v>
       </c>
@@ -2993,7 +2998,7 @@
       </c>
       <c r="K87" s="3"/>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A88" s="1">
         <v>45457</v>
       </c>
@@ -3018,7 +3023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A89" s="1">
         <v>45462</v>
       </c>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="K89" s="3"/>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A90" s="1">
         <v>45463</v>
       </c>
@@ -3070,7 +3075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A91" s="1">
         <v>45462</v>
       </c>
@@ -3096,7 +3101,7 @@
       </c>
       <c r="K91" s="3"/>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A92" s="1">
         <v>45463</v>
       </c>
@@ -3117,7 +3122,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A93" s="1">
         <v>45462</v>
       </c>
@@ -3149,7 +3154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A95" s="1">
         <v>45463</v>
       </c>
@@ -3173,7 +3178,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.75">
       <c r="A96" s="1">
         <v>45463</v>
       </c>
@@ -3194,7 +3199,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A97" s="1">
         <v>45463</v>
       </c>
@@ -3215,7 +3220,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A98" s="1">
         <v>45463</v>
       </c>
@@ -3240,7 +3245,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A99" s="1">
         <v>45463</v>
       </c>
@@ -3265,7 +3270,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A100" s="1">
         <v>45463</v>
       </c>
@@ -3290,7 +3295,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A101" s="1">
         <v>45484</v>
       </c>
@@ -3318,7 +3323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A102" s="1">
         <v>45484</v>
       </c>
@@ -3345,7 +3350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A103" s="1">
         <v>45484</v>
       </c>
@@ -3368,7 +3373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A104" s="1">
         <v>45484</v>
       </c>
@@ -3394,7 +3399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A105" s="1">
         <v>45484</v>
       </c>
@@ -3421,7 +3426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A106" s="1">
         <v>45484</v>
       </c>
@@ -3448,7 +3453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A107" s="1">
         <v>45484</v>
       </c>
@@ -3468,7 +3473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A108" s="1">
         <v>45484</v>
       </c>
@@ -3495,7 +3500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A109" s="1">
         <v>45484</v>
       </c>
@@ -3522,7 +3527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A110" s="1">
         <v>45484</v>
       </c>
@@ -3546,7 +3551,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A111" s="1">
         <v>45484</v>
       </c>
@@ -3563,7 +3568,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A112" s="1">
         <v>45484</v>
       </c>
@@ -3590,7 +3595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A113" s="1">
         <v>45484</v>
       </c>
@@ -3617,7 +3622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A114" s="1">
         <v>45484</v>
       </c>
@@ -3635,7 +3640,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A115" s="1">
         <v>45635</v>
       </c>
@@ -3666,7 +3671,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A116" s="1">
         <v>45635</v>
       </c>
@@ -3696,7 +3701,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A117" s="1">
         <v>45635</v>
       </c>
@@ -3723,7 +3728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A118" s="1">
         <v>45635</v>
       </c>
@@ -3750,7 +3755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A119" s="1">
         <v>45635</v>
       </c>
@@ -3781,7 +3786,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A120" s="1">
         <v>45635</v>
       </c>
@@ -3808,7 +3813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A121" s="1">
         <v>45635</v>
       </c>
@@ -3829,7 +3834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A122" s="1">
         <v>45635</v>
       </c>
@@ -3883,7 +3888,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A124" s="1">
         <v>45635</v>
       </c>
@@ -3910,7 +3915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A125" s="1">
         <v>45635</v>
       </c>
@@ -3941,7 +3946,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A126" s="1">
         <v>45635</v>
       </c>
@@ -3968,7 +3973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A127" s="1">
         <v>45635</v>
       </c>
@@ -3995,7 +4000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A128" s="1">
         <v>45635</v>
       </c>
@@ -4026,7 +4031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A129" s="1">
         <v>45635</v>
       </c>
@@ -4057,7 +4062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A130" s="1">
         <v>45635</v>
       </c>
@@ -4088,7 +4093,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A131" s="1">
         <v>45635</v>
       </c>
@@ -4119,7 +4124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A132" s="1">
         <v>45635</v>
       </c>
@@ -4146,7 +4151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A133" s="1">
         <v>45667</v>
       </c>
@@ -4171,7 +4176,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A134" s="1">
         <v>45667</v>
       </c>
@@ -4202,7 +4207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A135" s="1">
         <v>45667</v>
       </c>
@@ -4229,7 +4234,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A136" s="1">
         <v>45667</v>
       </c>
@@ -4256,7 +4261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A137" s="1">
         <v>45667</v>
       </c>
@@ -4287,7 +4292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A138" s="1">
         <v>45667</v>
       </c>
@@ -4314,7 +4319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A139" s="1">
         <v>45667</v>
       </c>
@@ -4338,7 +4343,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A140" s="1">
         <v>45667</v>
       </c>
@@ -4386,7 +4391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A142" s="1">
         <v>45667</v>
       </c>
@@ -4413,7 +4418,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A143" s="1">
         <v>45667</v>
       </c>
@@ -4444,7 +4449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A144" s="1">
         <v>45667</v>
       </c>
@@ -4471,7 +4476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A145" s="1">
         <v>45667</v>
       </c>
@@ -4488,7 +4493,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A146" s="1">
         <v>45667</v>
       </c>
@@ -4519,7 +4524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A147" s="1">
         <v>45667</v>
       </c>
@@ -4550,7 +4555,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A148" s="1">
         <v>45667</v>
       </c>
@@ -4581,7 +4586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A149" s="1">
         <v>45667</v>
       </c>
@@ -4615,7 +4620,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A150" s="1">
         <v>45667</v>
       </c>
@@ -4642,7 +4647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A151" s="1">
         <v>45502</v>
       </c>
@@ -4670,7 +4675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A152" s="1">
         <v>45502</v>
       </c>
@@ -4697,7 +4702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A153" s="1">
         <v>45502</v>
       </c>
@@ -4720,7 +4725,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A154" s="1">
         <v>45502</v>
       </c>
@@ -4747,7 +4752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A155" s="1">
         <v>45502</v>
       </c>
@@ -4774,7 +4779,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A156" s="1">
         <v>45502</v>
       </c>
@@ -4828,7 +4833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A158" s="1">
         <v>45502</v>
       </c>
@@ -4855,7 +4860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A159" s="1">
         <v>45502</v>
       </c>
@@ -4886,7 +4891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A160" s="1">
         <v>45502</v>
       </c>
@@ -4913,7 +4918,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A161" s="1">
         <v>45502</v>
       </c>
@@ -4927,7 +4932,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A162" s="1">
         <v>45502</v>
       </c>
@@ -4958,7 +4963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A163" s="1">
         <v>45502</v>
       </c>
@@ -4989,7 +4994,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A164" s="1">
         <v>45502</v>
       </c>
@@ -5020,7 +5025,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A165" s="1">
         <v>45502</v>
       </c>
@@ -5045,7 +5050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A166" s="1">
         <v>45534</v>
       </c>
@@ -5072,7 +5077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A167" s="1">
         <v>45534</v>
       </c>
@@ -5099,7 +5104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A168" s="1">
         <v>45534</v>
       </c>
@@ -5126,7 +5131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A169" s="1">
         <v>45534</v>
       </c>
@@ -5153,7 +5158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A170" s="1">
         <v>45534</v>
       </c>
@@ -5184,7 +5189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A171" s="1">
         <v>45534</v>
       </c>
@@ -5204,7 +5209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A172" s="1">
         <v>45534</v>
       </c>
@@ -5241,7 +5246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A174" s="1">
         <v>45534</v>
       </c>
@@ -5264,7 +5269,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A175" s="1">
         <v>45534</v>
       </c>
@@ -5291,7 +5296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A176" s="1">
         <v>45534</v>
       </c>
@@ -5314,7 +5319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A177" s="1">
         <v>45534</v>
       </c>
@@ -5338,7 +5343,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A178" s="1">
         <v>45534</v>
       </c>
@@ -5363,7 +5368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A179" s="1">
         <v>45534</v>
       </c>
@@ -5387,7 +5392,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A180" s="1">
         <v>45534</v>
       </c>
@@ -5411,7 +5416,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A181" s="1">
         <v>45534</v>
       </c>
@@ -5430,7 +5435,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A182" s="1">
         <v>45442</v>
       </c>
@@ -5455,7 +5460,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A183" s="1">
         <v>45442</v>
       </c>
@@ -5483,7 +5488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A184" s="1">
         <v>45442</v>
       </c>
@@ -5507,7 +5512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A185" s="1">
         <v>45442</v>
       </c>
@@ -5531,7 +5536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A186" s="1">
         <v>45442</v>
       </c>
@@ -5559,7 +5564,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A187" s="1">
         <v>45442</v>
       </c>
@@ -5598,7 +5603,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A189" s="1">
         <v>45442</v>
       </c>
@@ -5610,7 +5615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A190" s="1">
         <v>45442</v>
       </c>
@@ -5635,7 +5640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A191" s="1">
         <v>45442</v>
       </c>
@@ -5647,7 +5652,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A192" s="1">
         <v>45442</v>
       </c>
@@ -5662,7 +5667,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A193" s="1">
         <v>45442</v>
       </c>
@@ -5690,7 +5695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A194" s="1">
         <v>45442</v>
       </c>
@@ -5715,7 +5720,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A195" s="1">
         <v>45442</v>
       </c>
@@ -5743,7 +5748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A196" s="1">
         <v>45442</v>
       </c>
@@ -5771,7 +5776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A197" s="1">
         <v>45940</v>
       </c>
@@ -5802,7 +5807,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A198" s="1">
         <v>45940</v>
       </c>
@@ -5836,7 +5841,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A199" s="1">
         <v>45940</v>
       </c>
@@ -5863,7 +5868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A200" s="1">
         <v>45940</v>
       </c>
@@ -5893,7 +5898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A201" s="1">
         <v>45940</v>
       </c>
@@ -5927,7 +5932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A202" s="1">
         <v>45940</v>
       </c>
@@ -5957,7 +5962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A203" s="1">
         <v>45940</v>
       </c>
@@ -6008,7 +6013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A205" s="1">
         <v>45940</v>
       </c>
@@ -6029,7 +6034,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A206" s="1">
         <v>45940</v>
       </c>
@@ -6056,7 +6061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A207" s="1">
         <v>45940</v>
       </c>
@@ -6086,7 +6091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A208" s="1">
         <v>45940</v>
       </c>
@@ -6107,7 +6112,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A209" s="1">
         <v>45940</v>
       </c>
@@ -6132,7 +6137,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A210" s="1">
         <v>45940</v>
       </c>
@@ -6166,7 +6171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A211" s="1">
         <v>45940</v>
       </c>
@@ -6180,7 +6185,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A212" s="1">
         <v>45940</v>
       </c>
@@ -6205,7 +6210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A213" s="1">
         <v>45940</v>
       </c>
@@ -6235,7 +6240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A214" s="1">
         <v>45597</v>
       </c>
@@ -6262,7 +6267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A215" s="1">
         <v>45597</v>
       </c>
@@ -6289,7 +6294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A216" s="1">
         <v>45597</v>
       </c>
@@ -6316,7 +6321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A217" s="1">
         <v>45597</v>
       </c>
@@ -6343,7 +6348,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A218" s="1">
         <v>45597</v>
       </c>
@@ -6370,7 +6375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A219" s="1">
         <v>45597</v>
       </c>
@@ -6397,7 +6402,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A220" s="1">
         <v>45597</v>
       </c>
@@ -6447,7 +6452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A222" s="1">
         <v>45597</v>
       </c>
@@ -6461,7 +6466,7 @@
         <v>0.9</v>
       </c>
       <c r="E222">
-        <f t="shared" ref="E222:E229" si="15">C222-D222</f>
+        <f t="shared" ref="E222:E245" si="15">C222-D222</f>
         <v>-1.0000000000000009E-2</v>
       </c>
       <c r="G222">
@@ -6474,7 +6479,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A223" s="1">
         <v>45597</v>
       </c>
@@ -6501,7 +6506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A224" s="1">
         <v>45597</v>
       </c>
@@ -6528,7 +6533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A225" s="1">
         <v>45597</v>
       </c>
@@ -6555,7 +6560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A226" s="1">
         <v>45597</v>
       </c>
@@ -6582,7 +6587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A227" s="1">
         <v>45597</v>
       </c>
@@ -6609,7 +6614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A228" s="1">
         <v>45597</v>
       </c>
@@ -6636,7 +6641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.75">
       <c r="A229" s="1">
         <v>45597</v>
       </c>
@@ -6663,14 +6668,379 @@
         <v>8</v>
       </c>
     </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A230" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B230" t="s">
+        <v>2</v>
+      </c>
+      <c r="C230">
+        <v>0.495</v>
+      </c>
+      <c r="D230">
+        <v>1.65</v>
+      </c>
+      <c r="E230">
+        <v>-1.21</v>
+      </c>
+      <c r="J230" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A231" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B231" t="s">
+        <v>11</v>
+      </c>
+      <c r="C231">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="D231">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="E231">
+        <f t="shared" si="15"/>
+        <v>-0.45</v>
+      </c>
+      <c r="G231">
+        <v>21.9</v>
+      </c>
+      <c r="H231">
+        <v>5.61</v>
+      </c>
+      <c r="I231">
+        <v>3.66</v>
+      </c>
+      <c r="J231" t="s">
+        <v>8</v>
+      </c>
+      <c r="L231" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A232" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B232" t="s">
+        <v>12</v>
+      </c>
+      <c r="C232">
+        <v>0.755</v>
+      </c>
+      <c r="D232">
+        <v>1.23</v>
+      </c>
+      <c r="E232">
+        <f t="shared" si="15"/>
+        <v>-0.47499999999999998</v>
+      </c>
+      <c r="J232" t="s">
+        <v>8</v>
+      </c>
+      <c r="L232" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A233" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B233" t="s">
+        <v>13</v>
+      </c>
+      <c r="C233">
+        <v>0.24</v>
+      </c>
+      <c r="D233">
+        <v>1.2</v>
+      </c>
+      <c r="E233">
+        <f t="shared" si="15"/>
+        <v>-0.96</v>
+      </c>
+      <c r="G233">
+        <v>22.5</v>
+      </c>
+      <c r="H233">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I233">
+        <v>3.32</v>
+      </c>
+      <c r="J233" t="s">
+        <v>8</v>
+      </c>
+      <c r="L233" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A234" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B234" t="s">
+        <v>14</v>
+      </c>
+      <c r="C234">
+        <v>0.08</v>
+      </c>
+      <c r="D234">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E234">
+        <f t="shared" si="15"/>
+        <v>-0.44500000000000001</v>
+      </c>
+      <c r="G234">
+        <v>21</v>
+      </c>
+      <c r="H234">
+        <v>4</v>
+      </c>
+      <c r="I234">
+        <v>0.83</v>
+      </c>
+      <c r="J234" t="s">
+        <v>8</v>
+      </c>
+      <c r="L234" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A235" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B235" t="s">
+        <v>15</v>
+      </c>
+      <c r="C235">
+        <v>0.08</v>
+      </c>
+      <c r="D235">
+        <v>1.02</v>
+      </c>
+      <c r="E235">
+        <f t="shared" si="15"/>
+        <v>-0.94000000000000006</v>
+      </c>
+      <c r="G235">
+        <v>21.9</v>
+      </c>
+      <c r="H235">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="I235">
+        <v>3.17</v>
+      </c>
+      <c r="J235" t="s">
+        <v>8</v>
+      </c>
+      <c r="L235" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="A236" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B236" t="s">
+        <v>27</v>
+      </c>
+      <c r="C236">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="D236">
+        <v>1.33</v>
+      </c>
+      <c r="E236">
+        <f t="shared" si="15"/>
+        <v>-0.35500000000000009</v>
+      </c>
+      <c r="G236">
+        <v>19.8</v>
+      </c>
+      <c r="H236">
+        <v>5.3</v>
+      </c>
+      <c r="I236">
+        <v>0.6</v>
+      </c>
+      <c r="J236" t="s">
+        <v>8</v>
+      </c>
+      <c r="L236" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="B237" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237">
+        <v>0.18</v>
+      </c>
+      <c r="D237">
+        <v>1.395</v>
+      </c>
+      <c r="E237">
+        <f t="shared" si="15"/>
+        <v>-1.2150000000000001</v>
+      </c>
+      <c r="J237" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="B238" t="s">
+        <v>18</v>
+      </c>
+      <c r="C238">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="D238">
+        <v>3.02</v>
+      </c>
+      <c r="E238">
+        <f t="shared" si="15"/>
+        <v>-2.2149999999999999</v>
+      </c>
+      <c r="J238" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="B239" t="s">
+        <v>19</v>
+      </c>
+      <c r="C239">
+        <v>0.06</v>
+      </c>
+      <c r="D239">
+        <v>1.92</v>
+      </c>
+      <c r="E239">
+        <f t="shared" si="15"/>
+        <v>-1.8599999999999999</v>
+      </c>
+      <c r="J239" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.75">
+      <c r="B240" t="s">
+        <v>20</v>
+      </c>
+      <c r="C240">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="D240">
+        <v>3.08</v>
+      </c>
+      <c r="E240">
+        <f t="shared" si="15"/>
+        <v>-2.875</v>
+      </c>
+      <c r="J240" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="241" spans="2:10" x14ac:dyDescent="0.75">
+      <c r="B241" t="s">
+        <v>22</v>
+      </c>
+      <c r="C241">
+        <v>0.25</v>
+      </c>
+      <c r="D241">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E241">
+        <f t="shared" si="15"/>
+        <v>-0.87000000000000011</v>
+      </c>
+      <c r="J241" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="242" spans="2:10" x14ac:dyDescent="0.75">
+      <c r="B242" t="s">
+        <v>23</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>1.68</v>
+      </c>
+      <c r="E242">
+        <f t="shared" si="15"/>
+        <v>-1.68</v>
+      </c>
+      <c r="J242" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="243" spans="2:10" x14ac:dyDescent="0.75">
+      <c r="B243" t="s">
+        <v>24</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>1.04</v>
+      </c>
+      <c r="E243">
+        <f t="shared" si="15"/>
+        <v>-1.04</v>
+      </c>
+      <c r="J243" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="244" spans="2:10" x14ac:dyDescent="0.75">
+      <c r="B244" t="s">
+        <v>25</v>
+      </c>
+      <c r="C244">
+        <v>0.315</v>
+      </c>
+      <c r="D244">
+        <v>1.56</v>
+      </c>
+      <c r="E244">
+        <f t="shared" si="15"/>
+        <v>-1.2450000000000001</v>
+      </c>
+      <c r="J244" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="245" spans="2:10" x14ac:dyDescent="0.75">
+      <c r="B245" t="s">
+        <v>29</v>
+      </c>
+      <c r="C245">
+        <v>0.04</v>
+      </c>
+      <c r="D245">
+        <v>1.88</v>
+      </c>
+      <c r="E245">
+        <f t="shared" si="15"/>
+        <v>-1.8399999999999999</v>
+      </c>
+      <c r="J245" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L229" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="6GW1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L229" xr:uid="{D8F8C743-6008-44C7-8E48-24FED6FBC91C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
